--- a/document-merge-service/kt_so/templatefiles/pruefung-kanalisationsanschluss-und-versickerungsanlage.xlsx
+++ b/document-merge-service/kt_so/templatefiles/pruefung-kanalisationsanschluss-und-versickerungsanlage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\BJSVW\Agi\eBau\Dokumentenvorlagen\eBau\Systemvorlagen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72BAC62-7673-4EB3-9A6A-8BF12EA67B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E01795-19AA-46E4-B13C-7C4E5CB5EB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="645" windowWidth="25200" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2175" yWindow="210" windowWidth="27015" windowHeight="15045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vorprüfung gross" sheetId="1" r:id="rId1"/>
@@ -1030,21 +1030,6 @@
   </si>
   <si>
     <t>Wegbreite</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dossier-Nr.: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>{{ DOSSIER_NUMMER }}</t>
-    </r>
   </si>
   <si>
     <t>{{ BESCHREIBUNG_BAUVORHABEN }}</t>
@@ -1102,6 +1087,9 @@
     <t>{{ ALLE_GESUCHSTELLER_NAME_ADRESSE }}</t>
   </si>
   <si>
+    <t>Dossier-Nr.: {{ DOSSIER_NUMMER }}</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Grundstücksnummer: </t>
     </r>
@@ -1109,7 +1097,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF00B050"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -1125,7 +1112,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF00B050"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -1140,7 +1126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_ &quot;SFr.&quot;\ * #,##0.00_ ;_ &quot;SFr.&quot;\ * \-#,##0.00_ ;_ &quot;SFr.&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1266,20 +1252,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF00B050"/>
       <name val="Arial"/>
@@ -1287,16 +1259,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1634,7 +1599,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2154,196 +2119,204 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2641,26 +2614,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="186" t="s">
-        <v>266</v>
+      <c r="A1" s="17" t="s">
+        <v>265</v>
       </c>
       <c r="C1"/>
       <c r="D1"/>
       <c r="E1"/>
       <c r="F1"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="187"/>
+      <c r="J1" s="184"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="188" t="s">
-        <v>267</v>
+      <c r="A2" s="237" t="s">
+        <v>266</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
       <c r="E2"/>
       <c r="F2"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="189"/>
+      <c r="J2" s="185"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I3" s="3"/>
@@ -2694,68 +2667,68 @@
     </row>
     <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="B6" s="211" t="s">
+        <v>264</v>
+      </c>
+      <c r="B6" s="238" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6" s="239"/>
+      <c r="D6" s="239"/>
+      <c r="E6" s="239"/>
+      <c r="F6" s="239"/>
+      <c r="G6" s="239"/>
+      <c r="H6" s="239"/>
+      <c r="I6" s="240"/>
+      <c r="J6" s="11" t="s">
         <v>268</v>
-      </c>
-      <c r="C6" s="212"/>
-      <c r="D6" s="212"/>
-      <c r="E6" s="212"/>
-      <c r="F6" s="212"/>
-      <c r="G6" s="212"/>
-      <c r="H6" s="212"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="11" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="213" t="s">
-        <v>259</v>
-      </c>
-      <c r="C7" s="214"/>
-      <c r="D7" s="214"/>
-      <c r="E7" s="214"/>
-      <c r="F7" s="214"/>
-      <c r="G7" s="214"/>
-      <c r="H7" s="214"/>
-      <c r="I7" s="214"/>
+      <c r="B7" s="241" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" s="242"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="242"/>
+      <c r="F7" s="242"/>
+      <c r="G7" s="242"/>
+      <c r="H7" s="242"/>
+      <c r="I7" s="242"/>
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="213" t="s">
-        <v>260</v>
-      </c>
-      <c r="C8" s="215"/>
-      <c r="D8" s="215"/>
-      <c r="E8" s="215"/>
-      <c r="F8" s="215"/>
-      <c r="G8" s="215"/>
-      <c r="H8" s="215"/>
-      <c r="I8" s="215"/>
+      <c r="B8" s="241" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="243"/>
+      <c r="D8" s="243"/>
+      <c r="E8" s="243"/>
+      <c r="F8" s="243"/>
+      <c r="G8" s="243"/>
+      <c r="H8" s="243"/>
+      <c r="I8" s="243"/>
       <c r="J8" s="13"/>
     </row>
     <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="180" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="244" t="s">
         <v>261</v>
       </c>
-      <c r="B9" s="181" t="s">
-        <v>262</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="C9" s="245"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="245"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
       <c r="J9" s="13"/>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2835,35 +2808,35 @@
       <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="216" t="s">
+      <c r="A16" s="186" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="218" t="s">
+      <c r="B16" s="188" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="220" t="s">
+      <c r="C16" s="190" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="222" t="s">
+      <c r="D16" s="192" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="223"/>
-      <c r="F16" s="224"/>
-      <c r="G16" s="222" t="s">
+      <c r="E16" s="193"/>
+      <c r="F16" s="194"/>
+      <c r="G16" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="223"/>
-      <c r="I16" s="224"/>
-      <c r="J16" s="199" t="s">
+      <c r="H16" s="193"/>
+      <c r="I16" s="194"/>
+      <c r="J16" s="198" t="s">
         <v>10</v>
       </c>
-      <c r="K16" s="201"/>
-      <c r="L16" s="201"/>
+      <c r="K16" s="200"/>
+      <c r="L16" s="200"/>
     </row>
     <row r="17" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
-      <c r="B17" s="219"/>
-      <c r="C17" s="221"/>
+      <c r="A17" s="187"/>
+      <c r="B17" s="189"/>
+      <c r="C17" s="191"/>
       <c r="D17" s="18" t="s">
         <v>11</v>
       </c>
@@ -2882,9 +2855,9 @@
       <c r="I17" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="200"/>
-      <c r="K17" s="201"/>
-      <c r="L17" s="201"/>
+      <c r="J17" s="199"/>
+      <c r="K17" s="200"/>
+      <c r="L17" s="200"/>
     </row>
     <row r="18" spans="1:12" s="23" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
@@ -3470,28 +3443,28 @@
       <c r="I46" s="42"/>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="202"/>
-      <c r="B47" s="203"/>
-      <c r="C47" s="203"/>
-      <c r="D47" s="203"/>
-      <c r="E47" s="203"/>
-      <c r="F47" s="203"/>
-      <c r="G47" s="203"/>
-      <c r="H47" s="203"/>
-      <c r="I47" s="203"/>
-      <c r="J47" s="204"/>
+      <c r="A47" s="201"/>
+      <c r="B47" s="202"/>
+      <c r="C47" s="202"/>
+      <c r="D47" s="202"/>
+      <c r="E47" s="202"/>
+      <c r="F47" s="202"/>
+      <c r="G47" s="202"/>
+      <c r="H47" s="202"/>
+      <c r="I47" s="202"/>
+      <c r="J47" s="203"/>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="193"/>
-      <c r="B48" s="194"/>
-      <c r="C48" s="194"/>
-      <c r="D48" s="194"/>
-      <c r="E48" s="194"/>
-      <c r="F48" s="194"/>
-      <c r="G48" s="194"/>
-      <c r="H48" s="194"/>
-      <c r="I48" s="194"/>
-      <c r="J48" s="195"/>
+      <c r="A48" s="204"/>
+      <c r="B48" s="205"/>
+      <c r="C48" s="205"/>
+      <c r="D48" s="205"/>
+      <c r="E48" s="205"/>
+      <c r="F48" s="205"/>
+      <c r="G48" s="205"/>
+      <c r="H48" s="205"/>
+      <c r="I48" s="205"/>
+      <c r="J48" s="206"/>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="44"/>
@@ -3518,54 +3491,54 @@
       <c r="J50" s="46"/>
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="193"/>
-      <c r="B51" s="194"/>
-      <c r="C51" s="194"/>
-      <c r="D51" s="194"/>
-      <c r="E51" s="194"/>
-      <c r="F51" s="194"/>
-      <c r="G51" s="194"/>
-      <c r="H51" s="194"/>
-      <c r="I51" s="194"/>
-      <c r="J51" s="195"/>
+      <c r="A51" s="204"/>
+      <c r="B51" s="205"/>
+      <c r="C51" s="205"/>
+      <c r="D51" s="205"/>
+      <c r="E51" s="205"/>
+      <c r="F51" s="205"/>
+      <c r="G51" s="205"/>
+      <c r="H51" s="205"/>
+      <c r="I51" s="205"/>
+      <c r="J51" s="206"/>
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="193"/>
-      <c r="B52" s="194"/>
-      <c r="C52" s="194"/>
-      <c r="D52" s="194"/>
-      <c r="E52" s="194"/>
-      <c r="F52" s="194"/>
-      <c r="G52" s="194"/>
-      <c r="H52" s="194"/>
-      <c r="I52" s="194"/>
-      <c r="J52" s="195"/>
+      <c r="A52" s="204"/>
+      <c r="B52" s="205"/>
+      <c r="C52" s="205"/>
+      <c r="D52" s="205"/>
+      <c r="E52" s="205"/>
+      <c r="F52" s="205"/>
+      <c r="G52" s="205"/>
+      <c r="H52" s="205"/>
+      <c r="I52" s="205"/>
+      <c r="J52" s="206"/>
     </row>
     <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="193" t="s">
+      <c r="A53" s="204" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="194"/>
-      <c r="C53" s="194"/>
-      <c r="D53" s="194"/>
-      <c r="E53" s="194"/>
-      <c r="F53" s="194"/>
-      <c r="G53" s="194"/>
-      <c r="H53" s="194"/>
-      <c r="I53" s="194"/>
-      <c r="J53" s="195"/>
+      <c r="B53" s="205"/>
+      <c r="C53" s="205"/>
+      <c r="D53" s="205"/>
+      <c r="E53" s="205"/>
+      <c r="F53" s="205"/>
+      <c r="G53" s="205"/>
+      <c r="H53" s="205"/>
+      <c r="I53" s="205"/>
+      <c r="J53" s="206"/>
     </row>
     <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="205"/>
-      <c r="B54" s="206"/>
-      <c r="C54" s="206"/>
-      <c r="D54" s="206"/>
-      <c r="E54" s="206"/>
-      <c r="F54" s="206"/>
-      <c r="G54" s="206"/>
-      <c r="H54" s="206"/>
-      <c r="I54" s="206"/>
-      <c r="J54" s="207"/>
+      <c r="A54" s="207"/>
+      <c r="B54" s="208"/>
+      <c r="C54" s="208"/>
+      <c r="D54" s="208"/>
+      <c r="E54" s="208"/>
+      <c r="F54" s="208"/>
+      <c r="G54" s="208"/>
+      <c r="H54" s="208"/>
+      <c r="I54" s="208"/>
+      <c r="J54" s="209"/>
     </row>
     <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="47"/>
@@ -3602,15 +3575,15 @@
       <c r="A58" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="208"/>
-      <c r="C58" s="209"/>
-      <c r="D58" s="209"/>
-      <c r="E58" s="209"/>
-      <c r="F58" s="209"/>
-      <c r="G58" s="209"/>
-      <c r="H58" s="209"/>
-      <c r="I58" s="209"/>
-      <c r="J58" s="210"/>
+      <c r="B58" s="210"/>
+      <c r="C58" s="211"/>
+      <c r="D58" s="211"/>
+      <c r="E58" s="211"/>
+      <c r="F58" s="211"/>
+      <c r="G58" s="211"/>
+      <c r="H58" s="211"/>
+      <c r="I58" s="211"/>
+      <c r="J58" s="212"/>
       <c r="K58" s="23"/>
     </row>
     <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3783,64 +3756,64 @@
       <c r="I72" s="42"/>
     </row>
     <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="202"/>
-      <c r="B73" s="203"/>
-      <c r="C73" s="203"/>
-      <c r="D73" s="203"/>
-      <c r="E73" s="203"/>
-      <c r="F73" s="203"/>
-      <c r="G73" s="203"/>
-      <c r="H73" s="203"/>
-      <c r="I73" s="203"/>
-      <c r="J73" s="204"/>
+      <c r="A73" s="201"/>
+      <c r="B73" s="202"/>
+      <c r="C73" s="202"/>
+      <c r="D73" s="202"/>
+      <c r="E73" s="202"/>
+      <c r="F73" s="202"/>
+      <c r="G73" s="202"/>
+      <c r="H73" s="202"/>
+      <c r="I73" s="202"/>
+      <c r="J73" s="203"/>
     </row>
     <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="190"/>
-      <c r="B74" s="191"/>
-      <c r="C74" s="191"/>
-      <c r="D74" s="191"/>
-      <c r="E74" s="191"/>
-      <c r="F74" s="191"/>
-      <c r="G74" s="191"/>
-      <c r="H74" s="191"/>
-      <c r="I74" s="191"/>
-      <c r="J74" s="192"/>
+      <c r="A74" s="195"/>
+      <c r="B74" s="196"/>
+      <c r="C74" s="196"/>
+      <c r="D74" s="196"/>
+      <c r="E74" s="196"/>
+      <c r="F74" s="196"/>
+      <c r="G74" s="196"/>
+      <c r="H74" s="196"/>
+      <c r="I74" s="196"/>
+      <c r="J74" s="197"/>
     </row>
     <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="190"/>
-      <c r="B75" s="191"/>
-      <c r="C75" s="191"/>
-      <c r="D75" s="191"/>
-      <c r="E75" s="191"/>
-      <c r="F75" s="191"/>
-      <c r="G75" s="191"/>
-      <c r="H75" s="191"/>
-      <c r="I75" s="191"/>
-      <c r="J75" s="192"/>
+      <c r="A75" s="195"/>
+      <c r="B75" s="196"/>
+      <c r="C75" s="196"/>
+      <c r="D75" s="196"/>
+      <c r="E75" s="196"/>
+      <c r="F75" s="196"/>
+      <c r="G75" s="196"/>
+      <c r="H75" s="196"/>
+      <c r="I75" s="196"/>
+      <c r="J75" s="197"/>
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="190"/>
-      <c r="B76" s="191"/>
-      <c r="C76" s="191"/>
-      <c r="D76" s="191"/>
-      <c r="E76" s="191"/>
-      <c r="F76" s="191"/>
-      <c r="G76" s="191"/>
-      <c r="H76" s="191"/>
-      <c r="I76" s="191"/>
-      <c r="J76" s="192"/>
+      <c r="A76" s="195"/>
+      <c r="B76" s="196"/>
+      <c r="C76" s="196"/>
+      <c r="D76" s="196"/>
+      <c r="E76" s="196"/>
+      <c r="F76" s="196"/>
+      <c r="G76" s="196"/>
+      <c r="H76" s="196"/>
+      <c r="I76" s="196"/>
+      <c r="J76" s="197"/>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="190"/>
-      <c r="B77" s="191"/>
-      <c r="C77" s="191"/>
-      <c r="D77" s="191"/>
-      <c r="E77" s="191"/>
-      <c r="F77" s="191"/>
-      <c r="G77" s="191"/>
-      <c r="H77" s="191"/>
-      <c r="I77" s="191"/>
-      <c r="J77" s="192"/>
+      <c r="A77" s="195"/>
+      <c r="B77" s="196"/>
+      <c r="C77" s="196"/>
+      <c r="D77" s="196"/>
+      <c r="E77" s="196"/>
+      <c r="F77" s="196"/>
+      <c r="G77" s="196"/>
+      <c r="H77" s="196"/>
+      <c r="I77" s="196"/>
+      <c r="J77" s="197"/>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="54"/>
@@ -3855,30 +3828,30 @@
       <c r="J78" s="57"/>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="193" t="s">
+      <c r="A79" s="204" t="s">
         <v>60</v>
       </c>
-      <c r="B79" s="194"/>
-      <c r="C79" s="194"/>
-      <c r="D79" s="194"/>
-      <c r="E79" s="194"/>
-      <c r="F79" s="194"/>
-      <c r="G79" s="194"/>
-      <c r="H79" s="194"/>
-      <c r="I79" s="194"/>
-      <c r="J79" s="195"/>
+      <c r="B79" s="205"/>
+      <c r="C79" s="205"/>
+      <c r="D79" s="205"/>
+      <c r="E79" s="205"/>
+      <c r="F79" s="205"/>
+      <c r="G79" s="205"/>
+      <c r="H79" s="205"/>
+      <c r="I79" s="205"/>
+      <c r="J79" s="206"/>
     </row>
     <row r="80" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="196"/>
-      <c r="B80" s="197"/>
-      <c r="C80" s="197"/>
-      <c r="D80" s="197"/>
-      <c r="E80" s="197"/>
-      <c r="F80" s="197"/>
-      <c r="G80" s="197"/>
-      <c r="H80" s="197"/>
-      <c r="I80" s="197"/>
-      <c r="J80" s="198"/>
+      <c r="A80" s="213"/>
+      <c r="B80" s="214"/>
+      <c r="C80" s="214"/>
+      <c r="D80" s="214"/>
+      <c r="E80" s="214"/>
+      <c r="F80" s="214"/>
+      <c r="G80" s="214"/>
+      <c r="H80" s="214"/>
+      <c r="I80" s="214"/>
+      <c r="J80" s="215"/>
     </row>
     <row r="81" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="42"/>
@@ -3913,7 +3886,7 @@
         <v>74</v>
       </c>
       <c r="B85" s="58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C85" s="58"/>
       <c r="D85" s="58"/>
@@ -3939,8 +3912,8 @@
       <c r="A87" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="B87" s="182" t="s">
-        <v>264</v>
+      <c r="B87" s="181" t="s">
+        <v>263</v>
       </c>
       <c r="C87" s="59"/>
       <c r="D87" s="59"/>
@@ -6021,14 +5994,11 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A80:J80"/>
     <mergeCell ref="A74:J74"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -6041,11 +6011,14 @@
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="B58:J58"/>
     <mergeCell ref="A73:J73"/>
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A77:J77"/>
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6067,18 +6040,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="184"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="237" t="s">
         <v>266</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="187"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="188" t="s">
-        <v>267</v>
-      </c>
       <c r="I2" s="3"/>
-      <c r="J2" s="189"/>
+      <c r="J2" s="185"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I3" s="3"/>
@@ -6112,10 +6085,10 @@
     </row>
     <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="B6" s="246" t="s">
-        <v>268</v>
+        <v>264</v>
+      </c>
+      <c r="B6" s="247" t="s">
+        <v>267</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -6132,8 +6105,8 @@
       <c r="A7" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="185" t="s">
-        <v>259</v>
+      <c r="B7" s="248" t="s">
+        <v>258</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -6148,7 +6121,7 @@
       <c r="A8" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="246" t="s">
         <v>79</v>
       </c>
       <c r="C8" s="15"/>
@@ -6164,8 +6137,8 @@
       <c r="A9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="185" t="s">
-        <v>260</v>
+      <c r="B9" s="248" t="s">
+        <v>259</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
@@ -6174,7 +6147,7 @@
       <c r="G9" s="14"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="183" t="s">
+      <c r="J9" s="182" t="s">
         <v>269</v>
       </c>
     </row>
@@ -6192,7 +6165,7 @@
       <c r="G10" s="14"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="184" t="s">
+      <c r="J10" s="183" t="s">
         <v>270</v>
       </c>
     </row>
@@ -6209,35 +6182,35 @@
       <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="236" t="s">
+      <c r="A12" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="238" t="s">
+      <c r="B12" s="220" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="240" t="s">
+      <c r="C12" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="229" t="s">
+      <c r="D12" s="224" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="230"/>
-      <c r="F12" s="231"/>
-      <c r="G12" s="229" t="s">
+      <c r="E12" s="225"/>
+      <c r="F12" s="226"/>
+      <c r="G12" s="224" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="230"/>
-      <c r="I12" s="231"/>
-      <c r="J12" s="232" t="s">
+      <c r="H12" s="225"/>
+      <c r="I12" s="226"/>
+      <c r="J12" s="231" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="201"/>
-      <c r="L12" s="201"/>
+      <c r="K12" s="200"/>
+      <c r="L12" s="200"/>
     </row>
     <row r="13" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="237"/>
-      <c r="B13" s="239"/>
-      <c r="C13" s="241"/>
+      <c r="A13" s="219"/>
+      <c r="B13" s="221"/>
+      <c r="C13" s="223"/>
       <c r="D13" s="65" t="s">
         <v>11</v>
       </c>
@@ -6256,23 +6229,23 @@
       <c r="I13" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="233"/>
-      <c r="K13" s="201"/>
-      <c r="L13" s="201"/>
+      <c r="J13" s="232"/>
+      <c r="K13" s="200"/>
+      <c r="L13" s="200"/>
     </row>
     <row r="14" spans="1:12" s="66" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="225" t="s">
+      <c r="A14" s="227" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="225"/>
-      <c r="C14" s="225"/>
-      <c r="D14" s="225"/>
-      <c r="E14" s="225"/>
-      <c r="F14" s="225"/>
-      <c r="G14" s="225"/>
-      <c r="H14" s="225"/>
-      <c r="I14" s="225"/>
-      <c r="J14" s="225"/>
+      <c r="B14" s="227"/>
+      <c r="C14" s="227"/>
+      <c r="D14" s="227"/>
+      <c r="E14" s="227"/>
+      <c r="F14" s="227"/>
+      <c r="G14" s="227"/>
+      <c r="H14" s="227"/>
+      <c r="I14" s="227"/>
+      <c r="J14" s="227"/>
     </row>
     <row r="15" spans="1:12" s="71" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67" t="s">
@@ -6513,18 +6486,18 @@
       <c r="J25" s="78"/>
     </row>
     <row r="26" spans="1:10" s="71" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="226" t="s">
+      <c r="A26" s="228" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="226"/>
-      <c r="C26" s="226"/>
-      <c r="D26" s="226"/>
-      <c r="E26" s="226"/>
-      <c r="F26" s="226"/>
-      <c r="G26" s="226"/>
-      <c r="H26" s="226"/>
-      <c r="I26" s="226"/>
-      <c r="J26" s="226"/>
+      <c r="B26" s="228"/>
+      <c r="C26" s="228"/>
+      <c r="D26" s="228"/>
+      <c r="E26" s="228"/>
+      <c r="F26" s="228"/>
+      <c r="G26" s="228"/>
+      <c r="H26" s="228"/>
+      <c r="I26" s="228"/>
+      <c r="J26" s="228"/>
     </row>
     <row r="27" spans="1:10" s="71" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67" t="s">
@@ -7733,10 +7706,10 @@
       <c r="J88" s="28"/>
     </row>
     <row r="89" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="227" t="s">
+      <c r="A89" s="229" t="s">
         <v>204</v>
       </c>
-      <c r="B89" s="228"/>
+      <c r="B89" s="230"/>
       <c r="C89" s="149"/>
       <c r="D89" s="150"/>
       <c r="E89" s="150"/>
@@ -7747,14 +7720,14 @@
       <c r="J89" s="126"/>
     </row>
     <row r="90" spans="1:10" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="234" t="s">
+      <c r="A90" s="216" t="s">
         <v>205</v>
       </c>
-      <c r="B90" s="234"/>
-      <c r="C90" s="234"/>
-      <c r="D90" s="234"/>
-      <c r="E90" s="234"/>
-      <c r="F90" s="235"/>
+      <c r="B90" s="216"/>
+      <c r="C90" s="216"/>
+      <c r="D90" s="216"/>
+      <c r="E90" s="216"/>
+      <c r="F90" s="217"/>
       <c r="G90" s="30" t="s">
         <v>19</v>
       </c>
@@ -9325,11 +9298,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:F12"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="L12:L13"/>
     <mergeCell ref="A14:J14"/>
@@ -9337,6 +9305,11 @@
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="J12:J13"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9360,20 +9333,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="186" t="s">
-        <v>266</v>
+      <c r="A1" s="17" t="s">
+        <v>265</v>
       </c>
       <c r="G1" s="1"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="187"/>
+      <c r="J1" s="184"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="188" t="s">
-        <v>267</v>
+      <c r="A2" s="237" t="s">
+        <v>266</v>
       </c>
       <c r="G2" s="1"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="189"/>
+      <c r="J2" s="185"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I3" s="3"/>
@@ -9595,11 +9568,11 @@
       <c r="B17" s="76"/>
       <c r="C17" s="75"/>
       <c r="D17" s="75"/>
-      <c r="E17" s="242" t="s">
+      <c r="E17" s="233" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
+      <c r="F17" s="233"/>
+      <c r="G17" s="233"/>
       <c r="H17" s="173"/>
       <c r="I17" s="75"/>
       <c r="J17" s="75" t="s">
@@ -9759,19 +9732,19 @@
       <c r="J27" s="60"/>
     </row>
     <row r="28" spans="1:10" s="73" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="243" t="s">
+      <c r="A28" s="234" t="s">
         <v>245</v>
       </c>
-      <c r="B28" s="243"/>
+      <c r="B28" s="234"/>
       <c r="C28" s="175" t="s">
         <v>246</v>
       </c>
-      <c r="D28" s="243" t="s">
+      <c r="D28" s="234" t="s">
         <v>247</v>
       </c>
-      <c r="E28" s="243"/>
-      <c r="F28" s="243"/>
-      <c r="G28" s="243"/>
+      <c r="E28" s="234"/>
+      <c r="F28" s="234"/>
+      <c r="G28" s="234"/>
       <c r="I28" s="176" t="s">
         <v>246</v>
       </c>
@@ -9780,16 +9753,16 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="73" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="244" t="s">
+      <c r="A29" s="235" t="s">
         <v>248</v>
       </c>
-      <c r="B29" s="244"/>
-      <c r="D29" s="245">
+      <c r="B29" s="235"/>
+      <c r="D29" s="236">
         <v>113.8</v>
       </c>
-      <c r="E29" s="245"/>
-      <c r="F29" s="245"/>
-      <c r="G29" s="245"/>
+      <c r="E29" s="236"/>
+      <c r="F29" s="236"/>
+      <c r="G29" s="236"/>
     </row>
     <row r="30" spans="1:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="60"/>

--- a/document-merge-service/kt_so/templatefiles/pruefung-kanalisationsanschluss-und-versickerungsanlage.xlsx
+++ b/document-merge-service/kt_so/templatefiles/pruefung-kanalisationsanschluss-und-versickerungsanlage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\BJSVW\Agi\eBau\Dokumentenvorlagen\eBau\Systemvorlagen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\BJSVW\Agi\eBau\Dokumentenvorlagen\eBau\Systemvorlagen\Release15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E01795-19AA-46E4-B13C-7C4E5CB5EB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2758337C-4454-4282-8D8C-CFBE3D79AAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2175" yWindow="210" windowWidth="27015" windowHeight="15045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-40275" yWindow="-2400" windowWidth="38700" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vorprüfung gross" sheetId="1" r:id="rId1"/>
@@ -1030,9 +1030,6 @@
   </si>
   <si>
     <t>Wegbreite</t>
-  </si>
-  <si>
-    <t>{{ BESCHREIBUNG_BAUVORHABEN }}</t>
   </si>
   <si>
     <t>{{ ADRESSE }}</t>
@@ -1075,9 +1072,6 @@
     <t>{{ ZUSTAENDIG_NAME }}</t>
   </si>
   <si>
-    <t>Gesuchsteller/in</t>
-  </si>
-  <si>
     <t>{{ LEITBEHOERDE_NAME }}</t>
   </si>
   <si>
@@ -1117,6 +1111,12 @@
       </rPr>
       <t>{{ NUTZUNGSPLANUNG_GRUNDNUTZUNG }}</t>
     </r>
+  </si>
+  <si>
+    <t>{{ KURZBESCHREIBUNG_BAUVORHABEN }}</t>
+  </si>
+  <si>
+    <t>Gesuchsteller/in (Bauherrschaft)</t>
   </si>
 </sst>
 </file>
@@ -2132,6 +2132,103 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2159,68 +2256,32 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2246,33 +2307,6 @@
     <xf numFmtId="16" fontId="10" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="10" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2284,40 +2318,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2601,21 +2601,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L344"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="3.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="42.85546875" customWidth="1"/>
+    <col min="1" max="1" width="37.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="3.7265625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.26953125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.7265625" customWidth="1"/>
+    <col min="10" max="10" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C1"/>
       <c r="D1"/>
@@ -2624,9 +2624,9 @@
       <c r="I1" s="2"/>
       <c r="J1" s="184"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="237" t="s">
-        <v>266</v>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="186" t="s">
+        <v>264</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
@@ -2635,11 +2635,11 @@
       <c r="I2" s="3"/>
       <c r="J2" s="185"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I3" s="3"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
@@ -2653,7 +2653,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="9"/>
@@ -2665,73 +2665,73 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="B6" s="238" t="s">
-        <v>267</v>
-      </c>
-      <c r="C6" s="239"/>
-      <c r="D6" s="239"/>
-      <c r="E6" s="239"/>
-      <c r="F6" s="239"/>
-      <c r="G6" s="239"/>
-      <c r="H6" s="239"/>
-      <c r="I6" s="240"/>
+        <v>270</v>
+      </c>
+      <c r="B6" s="214" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="215"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="215"/>
+      <c r="F6" s="215"/>
+      <c r="G6" s="215"/>
+      <c r="H6" s="215"/>
+      <c r="I6" s="187"/>
       <c r="J6" s="11" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="241" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="242"/>
-      <c r="D7" s="242"/>
-      <c r="E7" s="242"/>
-      <c r="F7" s="242"/>
-      <c r="G7" s="242"/>
-      <c r="H7" s="242"/>
-      <c r="I7" s="242"/>
+      <c r="B7" s="216" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="217"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="217"/>
+      <c r="I7" s="217"/>
       <c r="J7" s="13"/>
     </row>
-    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="241" t="s">
+      <c r="B8" s="216" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" s="218"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="218"/>
+      <c r="G8" s="218"/>
+      <c r="H8" s="218"/>
+      <c r="I8" s="218"/>
+      <c r="J8" s="13"/>
+    </row>
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="180" t="s">
         <v>259</v>
       </c>
-      <c r="C8" s="243"/>
-      <c r="D8" s="243"/>
-      <c r="E8" s="243"/>
-      <c r="F8" s="243"/>
-      <c r="G8" s="243"/>
-      <c r="H8" s="243"/>
-      <c r="I8" s="243"/>
-      <c r="J8" s="13"/>
-    </row>
-    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="180" t="s">
+      <c r="B9" s="189" t="s">
         <v>260</v>
       </c>
-      <c r="B9" s="244" t="s">
-        <v>261</v>
-      </c>
-      <c r="C9" s="245"/>
-      <c r="D9" s="245"/>
-      <c r="E9" s="245"/>
-      <c r="F9" s="245"/>
-      <c r="G9" s="245"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
+      <c r="C9" s="190"/>
+      <c r="D9" s="190"/>
+      <c r="E9" s="190"/>
+      <c r="F9" s="190"/>
+      <c r="G9" s="190"/>
+      <c r="H9" s="191"/>
+      <c r="I9" s="191"/>
       <c r="J9" s="13"/>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
         <v>3</v>
       </c>
@@ -2747,7 +2747,7 @@
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
     </row>
-    <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="15"/>
       <c r="C11" s="14"/>
@@ -2759,7 +2759,7 @@
       <c r="I11" s="15"/>
       <c r="J11" s="13"/>
     </row>
-    <row r="12" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
@@ -2771,7 +2771,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
@@ -2783,7 +2783,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
@@ -2795,7 +2795,7 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
@@ -2807,36 +2807,36 @@
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="186" t="s">
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="219" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="188" t="s">
+      <c r="B16" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="190" t="s">
+      <c r="C16" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="192" t="s">
+      <c r="D16" s="225" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="193"/>
-      <c r="F16" s="194"/>
-      <c r="G16" s="192" t="s">
+      <c r="E16" s="226"/>
+      <c r="F16" s="227"/>
+      <c r="G16" s="225" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="193"/>
-      <c r="I16" s="194"/>
-      <c r="J16" s="198" t="s">
+      <c r="H16" s="226"/>
+      <c r="I16" s="227"/>
+      <c r="J16" s="202" t="s">
         <v>10</v>
       </c>
-      <c r="K16" s="200"/>
-      <c r="L16" s="200"/>
-    </row>
-    <row r="17" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="187"/>
-      <c r="B17" s="189"/>
-      <c r="C17" s="191"/>
+      <c r="K16" s="204"/>
+      <c r="L16" s="204"/>
+    </row>
+    <row r="17" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="220"/>
+      <c r="B17" s="222"/>
+      <c r="C17" s="224"/>
       <c r="D17" s="18" t="s">
         <v>11</v>
       </c>
@@ -2855,11 +2855,11 @@
       <c r="I17" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="199"/>
-      <c r="K17" s="200"/>
-      <c r="L17" s="200"/>
-    </row>
-    <row r="18" spans="1:12" s="23" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J17" s="203"/>
+      <c r="K17" s="204"/>
+      <c r="L17" s="204"/>
+    </row>
+    <row r="18" spans="1:12" s="23" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>17</v>
       </c>
@@ -2873,7 +2873,7 @@
       <c r="I18" s="21"/>
       <c r="J18" s="22"/>
     </row>
-    <row r="19" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="24" t="s">
         <v>18</v>
       </c>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="J19" s="28"/>
     </row>
-    <row r="20" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="24" t="s">
         <v>21</v>
       </c>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="J20" s="28"/>
     </row>
-    <row r="21" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="31" t="s">
         <v>22</v>
       </c>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="31" t="s">
         <v>23</v>
       </c>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="J22" s="28"/>
     </row>
-    <row r="23" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="24" t="s">
         <v>24</v>
       </c>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="J23" s="28"/>
     </row>
-    <row r="24" spans="1:12" s="29" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="29" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="32" t="s">
         <v>25</v>
       </c>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="J24" s="28"/>
     </row>
-    <row r="25" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="31" t="s">
         <v>26</v>
       </c>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="J25" s="28"/>
     </row>
-    <row r="26" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="31" t="s">
         <v>28</v>
       </c>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="J26" s="28"/>
     </row>
-    <row r="27" spans="1:12" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="24" t="s">
         <v>30</v>
       </c>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="J27" s="28"/>
     </row>
-    <row r="28" spans="1:12" s="29" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" s="29" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="32" t="s">
         <v>32</v>
       </c>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="J28" s="38"/>
     </row>
-    <row r="29" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="32" t="s">
         <v>34</v>
       </c>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="J29" s="28"/>
     </row>
-    <row r="30" spans="1:12" s="29" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" s="29" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="32" t="s">
         <v>36</v>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="J30" s="28"/>
     </row>
-    <row r="31" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="32" t="s">
         <v>38</v>
       </c>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="J31" s="28"/>
     </row>
-    <row r="32" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39" t="s">
         <v>40</v>
       </c>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="J32" s="28"/>
     </row>
-    <row r="33" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="31" t="s">
         <v>42</v>
       </c>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="J33" s="28"/>
     </row>
-    <row r="34" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="31" t="s">
         <v>44</v>
       </c>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="J34" s="28"/>
     </row>
-    <row r="35" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="31" t="s">
         <v>46</v>
       </c>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="J35" s="28"/>
     </row>
-    <row r="36" spans="1:11" s="29" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" s="29" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="39" t="s">
         <v>48</v>
       </c>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="J36" s="28"/>
     </row>
-    <row r="37" spans="1:11" s="29" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" s="29" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="39" t="s">
         <v>49</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="J37" s="28"/>
     </row>
-    <row r="38" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="24" t="s">
         <v>51</v>
       </c>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="J38" s="28"/>
     </row>
-    <row r="39" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="31" t="s">
         <v>52</v>
       </c>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="J39" s="28"/>
     </row>
-    <row r="40" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="31" t="s">
         <v>54</v>
       </c>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="J40" s="28"/>
     </row>
-    <row r="41" spans="1:11" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="39" t="s">
         <v>55</v>
       </c>
@@ -3389,7 +3389,7 @@
       <c r="I41" s="27"/>
       <c r="J41" s="28"/>
     </row>
-    <row r="42" spans="1:11" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="39" t="s">
         <v>57</v>
       </c>
@@ -3409,7 +3409,7 @@
       <c r="I42" s="27"/>
       <c r="J42" s="28"/>
     </row>
-    <row r="43" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="39" t="s">
         <v>58</v>
       </c>
@@ -3426,47 +3426,47 @@
       <c r="J43" s="28"/>
       <c r="K43" s="29"/>
     </row>
-    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H44" s="42"/>
       <c r="I44" s="42"/>
       <c r="K44" s="29"/>
     </row>
-    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="43" t="s">
         <v>59</v>
       </c>
       <c r="H45" s="42"/>
       <c r="I45" s="42"/>
     </row>
-    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H46" s="42"/>
       <c r="I46" s="42"/>
     </row>
-    <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="201"/>
-      <c r="B47" s="202"/>
-      <c r="C47" s="202"/>
-      <c r="D47" s="202"/>
-      <c r="E47" s="202"/>
-      <c r="F47" s="202"/>
-      <c r="G47" s="202"/>
-      <c r="H47" s="202"/>
-      <c r="I47" s="202"/>
-      <c r="J47" s="203"/>
-    </row>
-    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="204"/>
-      <c r="B48" s="205"/>
-      <c r="C48" s="205"/>
-      <c r="D48" s="205"/>
-      <c r="E48" s="205"/>
-      <c r="F48" s="205"/>
-      <c r="G48" s="205"/>
-      <c r="H48" s="205"/>
-      <c r="I48" s="205"/>
-      <c r="J48" s="206"/>
-    </row>
-    <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="205"/>
+      <c r="B47" s="206"/>
+      <c r="C47" s="206"/>
+      <c r="D47" s="206"/>
+      <c r="E47" s="206"/>
+      <c r="F47" s="206"/>
+      <c r="G47" s="206"/>
+      <c r="H47" s="206"/>
+      <c r="I47" s="206"/>
+      <c r="J47" s="207"/>
+    </row>
+    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="196"/>
+      <c r="B48" s="197"/>
+      <c r="C48" s="197"/>
+      <c r="D48" s="197"/>
+      <c r="E48" s="197"/>
+      <c r="F48" s="197"/>
+      <c r="G48" s="197"/>
+      <c r="H48" s="197"/>
+      <c r="I48" s="197"/>
+      <c r="J48" s="198"/>
+    </row>
+    <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="44"/>
       <c r="B49" s="45"/>
       <c r="C49" s="45"/>
@@ -3478,7 +3478,7 @@
       <c r="I49" s="45"/>
       <c r="J49" s="46"/>
     </row>
-    <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="44"/>
       <c r="B50" s="45"/>
       <c r="C50" s="45"/>
@@ -3490,57 +3490,57 @@
       <c r="I50" s="45"/>
       <c r="J50" s="46"/>
     </row>
-    <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="204"/>
-      <c r="B51" s="205"/>
-      <c r="C51" s="205"/>
-      <c r="D51" s="205"/>
-      <c r="E51" s="205"/>
-      <c r="F51" s="205"/>
-      <c r="G51" s="205"/>
-      <c r="H51" s="205"/>
-      <c r="I51" s="205"/>
-      <c r="J51" s="206"/>
-    </row>
-    <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="204"/>
-      <c r="B52" s="205"/>
-      <c r="C52" s="205"/>
-      <c r="D52" s="205"/>
-      <c r="E52" s="205"/>
-      <c r="F52" s="205"/>
-      <c r="G52" s="205"/>
-      <c r="H52" s="205"/>
-      <c r="I52" s="205"/>
-      <c r="J52" s="206"/>
-    </row>
-    <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="204" t="s">
+    <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="196"/>
+      <c r="B51" s="197"/>
+      <c r="C51" s="197"/>
+      <c r="D51" s="197"/>
+      <c r="E51" s="197"/>
+      <c r="F51" s="197"/>
+      <c r="G51" s="197"/>
+      <c r="H51" s="197"/>
+      <c r="I51" s="197"/>
+      <c r="J51" s="198"/>
+    </row>
+    <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="196"/>
+      <c r="B52" s="197"/>
+      <c r="C52" s="197"/>
+      <c r="D52" s="197"/>
+      <c r="E52" s="197"/>
+      <c r="F52" s="197"/>
+      <c r="G52" s="197"/>
+      <c r="H52" s="197"/>
+      <c r="I52" s="197"/>
+      <c r="J52" s="198"/>
+    </row>
+    <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="196" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="205"/>
-      <c r="C53" s="205"/>
-      <c r="D53" s="205"/>
-      <c r="E53" s="205"/>
-      <c r="F53" s="205"/>
-      <c r="G53" s="205"/>
-      <c r="H53" s="205"/>
-      <c r="I53" s="205"/>
-      <c r="J53" s="206"/>
-    </row>
-    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="207"/>
-      <c r="B54" s="208"/>
-      <c r="C54" s="208"/>
-      <c r="D54" s="208"/>
-      <c r="E54" s="208"/>
-      <c r="F54" s="208"/>
-      <c r="G54" s="208"/>
-      <c r="H54" s="208"/>
-      <c r="I54" s="208"/>
-      <c r="J54" s="209"/>
-    </row>
-    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="197"/>
+      <c r="C53" s="197"/>
+      <c r="D53" s="197"/>
+      <c r="E53" s="197"/>
+      <c r="F53" s="197"/>
+      <c r="G53" s="197"/>
+      <c r="H53" s="197"/>
+      <c r="I53" s="197"/>
+      <c r="J53" s="198"/>
+    </row>
+    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="208"/>
+      <c r="B54" s="209"/>
+      <c r="C54" s="209"/>
+      <c r="D54" s="209"/>
+      <c r="E54" s="209"/>
+      <c r="F54" s="209"/>
+      <c r="G54" s="209"/>
+      <c r="H54" s="209"/>
+      <c r="I54" s="209"/>
+      <c r="J54" s="210"/>
+    </row>
+    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="47"/>
       <c r="B55" s="47"/>
       <c r="C55" s="47"/>
@@ -3552,7 +3552,7 @@
       <c r="I55" s="47"/>
       <c r="J55" s="47"/>
     </row>
-    <row r="56" spans="1:11" s="23" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" s="23" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="19" t="s">
         <v>61</v>
       </c>
@@ -3567,30 +3567,30 @@
       <c r="J56" s="22"/>
       <c r="K56"/>
     </row>
-    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H57" s="42"/>
       <c r="I57" s="42"/>
     </row>
-    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="210"/>
-      <c r="C58" s="211"/>
-      <c r="D58" s="211"/>
-      <c r="E58" s="211"/>
-      <c r="F58" s="211"/>
-      <c r="G58" s="211"/>
-      <c r="H58" s="211"/>
-      <c r="I58" s="211"/>
-      <c r="J58" s="212"/>
+      <c r="B58" s="211"/>
+      <c r="C58" s="212"/>
+      <c r="D58" s="212"/>
+      <c r="E58" s="212"/>
+      <c r="F58" s="212"/>
+      <c r="G58" s="212"/>
+      <c r="H58" s="212"/>
+      <c r="I58" s="212"/>
+      <c r="J58" s="213"/>
       <c r="K58" s="23"/>
     </row>
-    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H59" s="42"/>
       <c r="I59" s="42"/>
     </row>
-    <row r="60" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="48" t="s">
         <v>63</v>
       </c>
@@ -3607,7 +3607,7 @@
       <c r="J60" s="50"/>
       <c r="K60"/>
     </row>
-    <row r="61" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="48" t="s">
         <v>64</v>
       </c>
@@ -3624,7 +3624,7 @@
       <c r="J61" s="51"/>
       <c r="K61"/>
     </row>
-    <row r="62" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="48" t="s">
         <v>65</v>
       </c>
@@ -3638,7 +3638,7 @@
       <c r="I62" s="49"/>
       <c r="J62" s="52"/>
     </row>
-    <row r="63" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="48" t="s">
         <v>66</v>
       </c>
@@ -3652,7 +3652,7 @@
       <c r="I63" s="49"/>
       <c r="J63" s="52"/>
     </row>
-    <row r="64" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="48" t="s">
         <v>67</v>
       </c>
@@ -3668,7 +3668,7 @@
       <c r="I64" s="49"/>
       <c r="J64" s="52"/>
     </row>
-    <row r="65" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="48" t="s">
         <v>69</v>
       </c>
@@ -3682,7 +3682,7 @@
       <c r="I65" s="49"/>
       <c r="J65" s="52"/>
     </row>
-    <row r="66" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="48" t="s">
         <v>70</v>
       </c>
@@ -3696,7 +3696,7 @@
       <c r="I66" s="48"/>
       <c r="J66" s="52"/>
     </row>
-    <row r="67" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="48" t="s">
         <v>71</v>
       </c>
@@ -3710,7 +3710,7 @@
       <c r="I67" s="48"/>
       <c r="J67" s="52"/>
     </row>
-    <row r="68" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="48" t="s">
         <v>72</v>
       </c>
@@ -3724,7 +3724,7 @@
       <c r="I68" s="48"/>
       <c r="J68" s="52"/>
     </row>
-    <row r="69" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="48" t="s">
         <v>73</v>
       </c>
@@ -3737,85 +3737,85 @@
       <c r="H69" s="48"/>
       <c r="I69" s="48"/>
     </row>
-    <row r="70" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C70" s="42"/>
       <c r="D70" s="42"/>
       <c r="E70" s="42"/>
       <c r="F70" s="42"/>
       <c r="G70" s="42"/>
     </row>
-    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="53" t="s">
         <v>59</v>
       </c>
       <c r="H71" s="42"/>
       <c r="I71" s="42"/>
     </row>
-    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H72" s="42"/>
       <c r="I72" s="42"/>
     </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="201"/>
-      <c r="B73" s="202"/>
-      <c r="C73" s="202"/>
-      <c r="D73" s="202"/>
-      <c r="E73" s="202"/>
-      <c r="F73" s="202"/>
-      <c r="G73" s="202"/>
-      <c r="H73" s="202"/>
-      <c r="I73" s="202"/>
-      <c r="J73" s="203"/>
-    </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="195"/>
-      <c r="B74" s="196"/>
-      <c r="C74" s="196"/>
-      <c r="D74" s="196"/>
-      <c r="E74" s="196"/>
-      <c r="F74" s="196"/>
-      <c r="G74" s="196"/>
-      <c r="H74" s="196"/>
-      <c r="I74" s="196"/>
-      <c r="J74" s="197"/>
-    </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="195"/>
-      <c r="B75" s="196"/>
-      <c r="C75" s="196"/>
-      <c r="D75" s="196"/>
-      <c r="E75" s="196"/>
-      <c r="F75" s="196"/>
-      <c r="G75" s="196"/>
-      <c r="H75" s="196"/>
-      <c r="I75" s="196"/>
-      <c r="J75" s="197"/>
-    </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="195"/>
-      <c r="B76" s="196"/>
-      <c r="C76" s="196"/>
-      <c r="D76" s="196"/>
-      <c r="E76" s="196"/>
-      <c r="F76" s="196"/>
-      <c r="G76" s="196"/>
-      <c r="H76" s="196"/>
-      <c r="I76" s="196"/>
-      <c r="J76" s="197"/>
-    </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="195"/>
-      <c r="B77" s="196"/>
-      <c r="C77" s="196"/>
-      <c r="D77" s="196"/>
-      <c r="E77" s="196"/>
-      <c r="F77" s="196"/>
-      <c r="G77" s="196"/>
-      <c r="H77" s="196"/>
-      <c r="I77" s="196"/>
-      <c r="J77" s="197"/>
-    </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="205"/>
+      <c r="B73" s="206"/>
+      <c r="C73" s="206"/>
+      <c r="D73" s="206"/>
+      <c r="E73" s="206"/>
+      <c r="F73" s="206"/>
+      <c r="G73" s="206"/>
+      <c r="H73" s="206"/>
+      <c r="I73" s="206"/>
+      <c r="J73" s="207"/>
+    </row>
+    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="193"/>
+      <c r="B74" s="194"/>
+      <c r="C74" s="194"/>
+      <c r="D74" s="194"/>
+      <c r="E74" s="194"/>
+      <c r="F74" s="194"/>
+      <c r="G74" s="194"/>
+      <c r="H74" s="194"/>
+      <c r="I74" s="194"/>
+      <c r="J74" s="195"/>
+    </row>
+    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="193"/>
+      <c r="B75" s="194"/>
+      <c r="C75" s="194"/>
+      <c r="D75" s="194"/>
+      <c r="E75" s="194"/>
+      <c r="F75" s="194"/>
+      <c r="G75" s="194"/>
+      <c r="H75" s="194"/>
+      <c r="I75" s="194"/>
+      <c r="J75" s="195"/>
+    </row>
+    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="193"/>
+      <c r="B76" s="194"/>
+      <c r="C76" s="194"/>
+      <c r="D76" s="194"/>
+      <c r="E76" s="194"/>
+      <c r="F76" s="194"/>
+      <c r="G76" s="194"/>
+      <c r="H76" s="194"/>
+      <c r="I76" s="194"/>
+      <c r="J76" s="195"/>
+    </row>
+    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="193"/>
+      <c r="B77" s="194"/>
+      <c r="C77" s="194"/>
+      <c r="D77" s="194"/>
+      <c r="E77" s="194"/>
+      <c r="F77" s="194"/>
+      <c r="G77" s="194"/>
+      <c r="H77" s="194"/>
+      <c r="I77" s="194"/>
+      <c r="J77" s="195"/>
+    </row>
+    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="54"/>
       <c r="B78" s="55"/>
       <c r="C78" s="56"/>
@@ -3827,66 +3827,66 @@
       <c r="I78" s="55"/>
       <c r="J78" s="57"/>
     </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="204" t="s">
+    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="196" t="s">
         <v>60</v>
       </c>
-      <c r="B79" s="205"/>
-      <c r="C79" s="205"/>
-      <c r="D79" s="205"/>
-      <c r="E79" s="205"/>
-      <c r="F79" s="205"/>
-      <c r="G79" s="205"/>
-      <c r="H79" s="205"/>
-      <c r="I79" s="205"/>
-      <c r="J79" s="206"/>
-    </row>
-    <row r="80" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="213"/>
-      <c r="B80" s="214"/>
-      <c r="C80" s="214"/>
-      <c r="D80" s="214"/>
-      <c r="E80" s="214"/>
-      <c r="F80" s="214"/>
-      <c r="G80" s="214"/>
-      <c r="H80" s="214"/>
-      <c r="I80" s="214"/>
-      <c r="J80" s="215"/>
-    </row>
-    <row r="81" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="197"/>
+      <c r="C79" s="197"/>
+      <c r="D79" s="197"/>
+      <c r="E79" s="197"/>
+      <c r="F79" s="197"/>
+      <c r="G79" s="197"/>
+      <c r="H79" s="197"/>
+      <c r="I79" s="197"/>
+      <c r="J79" s="198"/>
+    </row>
+    <row r="80" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="199"/>
+      <c r="B80" s="200"/>
+      <c r="C80" s="200"/>
+      <c r="D80" s="200"/>
+      <c r="E80" s="200"/>
+      <c r="F80" s="200"/>
+      <c r="G80" s="200"/>
+      <c r="H80" s="200"/>
+      <c r="I80" s="200"/>
+      <c r="J80" s="201"/>
+    </row>
+    <row r="81" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C81" s="42"/>
       <c r="D81" s="42"/>
       <c r="E81" s="42"/>
       <c r="F81" s="42"/>
       <c r="G81" s="42"/>
     </row>
-    <row r="82" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C82" s="42"/>
       <c r="D82" s="42"/>
       <c r="E82" s="42"/>
       <c r="F82" s="42"/>
       <c r="G82" s="42"/>
     </row>
-    <row r="83" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C83" s="42"/>
       <c r="D83" s="42"/>
       <c r="E83" s="42"/>
       <c r="F83" s="42"/>
       <c r="G83" s="42"/>
     </row>
-    <row r="84" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C84" s="42"/>
       <c r="D84" s="42"/>
       <c r="E84" s="42"/>
       <c r="F84" s="42"/>
       <c r="G84" s="42"/>
     </row>
-    <row r="85" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="58" t="s">
         <v>74</v>
       </c>
       <c r="B85" s="58" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C85" s="58"/>
       <c r="D85" s="58"/>
@@ -3897,7 +3897,7 @@
       <c r="I85" s="60"/>
       <c r="J85" s="60"/>
     </row>
-    <row r="86" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="58"/>
       <c r="C86" s="59"/>
       <c r="D86" s="59"/>
@@ -3908,12 +3908,12 @@
       <c r="I86" s="60"/>
       <c r="J86" s="60"/>
     </row>
-    <row r="87" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="58" t="s">
         <v>75</v>
       </c>
       <c r="B87" s="181" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C87" s="59"/>
       <c r="D87" s="59"/>
@@ -3924,7 +3924,7 @@
       <c r="I87" s="60"/>
       <c r="J87" s="60"/>
     </row>
-    <row r="88" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="60"/>
       <c r="C88" s="59"/>
       <c r="D88" s="59"/>
@@ -3935,7 +3935,7 @@
       <c r="I88" s="60"/>
       <c r="J88" s="60"/>
     </row>
-    <row r="89" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="60"/>
       <c r="C89" s="59"/>
       <c r="D89" s="59"/>
@@ -3946,7 +3946,7 @@
       <c r="I89" s="60"/>
       <c r="J89" s="60"/>
     </row>
-    <row r="90" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B90" s="60"/>
       <c r="C90" s="59"/>
       <c r="D90" s="59"/>
@@ -3957,7 +3957,7 @@
       <c r="I90" s="60"/>
       <c r="J90" s="60"/>
     </row>
-    <row r="91" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B91" s="60"/>
       <c r="C91" s="59"/>
       <c r="D91" s="59"/>
@@ -3968,7 +3968,7 @@
       <c r="I91" s="60"/>
       <c r="J91" s="60"/>
     </row>
-    <row r="92" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B92" s="60"/>
       <c r="C92" s="59"/>
       <c r="D92" s="59"/>
@@ -3979,7 +3979,7 @@
       <c r="I92" s="60"/>
       <c r="J92" s="60"/>
     </row>
-    <row r="93" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B93" s="60"/>
       <c r="C93" s="59"/>
       <c r="D93" s="59"/>
@@ -3990,7 +3990,7 @@
       <c r="I93" s="60"/>
       <c r="J93" s="60"/>
     </row>
-    <row r="94" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B94" s="60"/>
       <c r="C94" s="59"/>
       <c r="D94" s="59"/>
@@ -4001,7 +4001,7 @@
       <c r="I94" s="60"/>
       <c r="J94" s="60"/>
     </row>
-    <row r="95" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B95" s="60"/>
       <c r="C95" s="59"/>
       <c r="D95" s="59"/>
@@ -4012,7 +4012,7 @@
       <c r="I95" s="60"/>
       <c r="J95" s="60"/>
     </row>
-    <row r="96" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B96" s="60"/>
       <c r="C96" s="59"/>
       <c r="D96" s="59"/>
@@ -4023,7 +4023,7 @@
       <c r="I96" s="60"/>
       <c r="J96" s="60"/>
     </row>
-    <row r="97" spans="2:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B97" s="60"/>
       <c r="C97" s="59"/>
       <c r="D97" s="59"/>
@@ -4034,7 +4034,7 @@
       <c r="I97" s="60"/>
       <c r="J97" s="60"/>
     </row>
-    <row r="98" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="60"/>
       <c r="C98" s="59"/>
       <c r="D98" s="59"/>
@@ -4045,7 +4045,7 @@
       <c r="I98" s="60"/>
       <c r="J98" s="60"/>
     </row>
-    <row r="99" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B99" s="60"/>
       <c r="C99" s="59"/>
       <c r="D99" s="59"/>
@@ -4056,7 +4056,7 @@
       <c r="I99" s="60"/>
       <c r="J99" s="60"/>
     </row>
-    <row r="100" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B100" s="60"/>
       <c r="C100" s="59"/>
       <c r="D100" s="59"/>
@@ -4067,7 +4067,7 @@
       <c r="I100" s="60"/>
       <c r="J100" s="60"/>
     </row>
-    <row r="101" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B101" s="60"/>
       <c r="C101" s="59"/>
       <c r="D101" s="59"/>
@@ -4078,7 +4078,7 @@
       <c r="I101" s="60"/>
       <c r="J101" s="60"/>
     </row>
-    <row r="102" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B102" s="60"/>
       <c r="C102" s="59"/>
       <c r="D102" s="59"/>
@@ -4089,7 +4089,7 @@
       <c r="I102" s="60"/>
       <c r="J102" s="60"/>
     </row>
-    <row r="103" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B103" s="60"/>
       <c r="C103" s="59"/>
       <c r="D103" s="59"/>
@@ -4100,7 +4100,7 @@
       <c r="I103" s="60"/>
       <c r="J103" s="60"/>
     </row>
-    <row r="104" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="60"/>
       <c r="C104" s="59"/>
       <c r="D104" s="59"/>
@@ -4111,7 +4111,7 @@
       <c r="I104" s="60"/>
       <c r="J104" s="60"/>
     </row>
-    <row r="105" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B105" s="60"/>
       <c r="C105" s="59"/>
       <c r="D105" s="59"/>
@@ -4122,7 +4122,7 @@
       <c r="I105" s="60"/>
       <c r="J105" s="60"/>
     </row>
-    <row r="106" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B106" s="60"/>
       <c r="C106" s="59"/>
       <c r="D106" s="59"/>
@@ -4133,7 +4133,7 @@
       <c r="I106" s="60"/>
       <c r="J106" s="60"/>
     </row>
-    <row r="107" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B107" s="60"/>
       <c r="C107" s="59"/>
       <c r="D107" s="59"/>
@@ -4144,7 +4144,7 @@
       <c r="I107" s="60"/>
       <c r="J107" s="60"/>
     </row>
-    <row r="108" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B108" s="60"/>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -4155,7 +4155,7 @@
       <c r="I108" s="60"/>
       <c r="J108" s="60"/>
     </row>
-    <row r="109" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B109" s="60"/>
       <c r="C109" s="59"/>
       <c r="D109" s="59"/>
@@ -4166,7 +4166,7 @@
       <c r="I109" s="60"/>
       <c r="J109" s="60"/>
     </row>
-    <row r="110" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B110" s="60"/>
       <c r="C110" s="59"/>
       <c r="D110" s="59"/>
@@ -4177,7 +4177,7 @@
       <c r="I110" s="60"/>
       <c r="J110" s="60"/>
     </row>
-    <row r="111" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B111" s="60"/>
       <c r="C111" s="59"/>
       <c r="D111" s="59"/>
@@ -4188,7 +4188,7 @@
       <c r="I111" s="60"/>
       <c r="J111" s="60"/>
     </row>
-    <row r="112" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B112" s="60"/>
       <c r="C112" s="59"/>
       <c r="D112" s="59"/>
@@ -4199,7 +4199,7 @@
       <c r="I112" s="60"/>
       <c r="J112" s="60"/>
     </row>
-    <row r="113" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B113" s="60"/>
       <c r="C113" s="59"/>
       <c r="D113" s="59"/>
@@ -4210,7 +4210,7 @@
       <c r="I113" s="60"/>
       <c r="J113" s="60"/>
     </row>
-    <row r="114" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="60"/>
       <c r="C114" s="59"/>
       <c r="D114" s="59"/>
@@ -4221,7 +4221,7 @@
       <c r="I114" s="60"/>
       <c r="J114" s="60"/>
     </row>
-    <row r="115" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="60"/>
       <c r="C115" s="59"/>
       <c r="D115" s="59"/>
@@ -4232,7 +4232,7 @@
       <c r="I115" s="60"/>
       <c r="J115" s="60"/>
     </row>
-    <row r="116" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B116" s="60"/>
       <c r="C116" s="59"/>
       <c r="D116" s="59"/>
@@ -4243,7 +4243,7 @@
       <c r="I116" s="60"/>
       <c r="J116" s="60"/>
     </row>
-    <row r="117" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B117" s="60"/>
       <c r="C117" s="59"/>
       <c r="D117" s="59"/>
@@ -4254,7 +4254,7 @@
       <c r="I117" s="60"/>
       <c r="J117" s="60"/>
     </row>
-    <row r="118" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B118" s="60"/>
       <c r="C118" s="59"/>
       <c r="D118" s="59"/>
@@ -4265,7 +4265,7 @@
       <c r="I118" s="60"/>
       <c r="J118" s="60"/>
     </row>
-    <row r="119" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B119" s="60"/>
       <c r="C119" s="59"/>
       <c r="D119" s="59"/>
@@ -4276,7 +4276,7 @@
       <c r="I119" s="60"/>
       <c r="J119" s="60"/>
     </row>
-    <row r="120" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="60"/>
       <c r="C120" s="59"/>
       <c r="D120" s="59"/>
@@ -4287,7 +4287,7 @@
       <c r="I120" s="60"/>
       <c r="J120" s="60"/>
     </row>
-    <row r="121" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B121" s="60"/>
       <c r="C121" s="59"/>
       <c r="D121" s="59"/>
@@ -4298,7 +4298,7 @@
       <c r="I121" s="60"/>
       <c r="J121" s="60"/>
     </row>
-    <row r="122" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B122" s="60"/>
       <c r="C122" s="59"/>
       <c r="D122" s="59"/>
@@ -4309,7 +4309,7 @@
       <c r="I122" s="60"/>
       <c r="J122" s="60"/>
     </row>
-    <row r="123" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B123" s="60"/>
       <c r="C123" s="59"/>
       <c r="D123" s="59"/>
@@ -4320,7 +4320,7 @@
       <c r="I123" s="60"/>
       <c r="J123" s="60"/>
     </row>
-    <row r="124" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B124" s="60"/>
       <c r="C124" s="59"/>
       <c r="D124" s="59"/>
@@ -4331,7 +4331,7 @@
       <c r="I124" s="60"/>
       <c r="J124" s="60"/>
     </row>
-    <row r="125" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B125" s="60"/>
       <c r="C125" s="59"/>
       <c r="D125" s="59"/>
@@ -4342,7 +4342,7 @@
       <c r="I125" s="60"/>
       <c r="J125" s="60"/>
     </row>
-    <row r="126" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="60"/>
       <c r="C126" s="59"/>
       <c r="D126" s="59"/>
@@ -4353,7 +4353,7 @@
       <c r="I126" s="60"/>
       <c r="J126" s="60"/>
     </row>
-    <row r="127" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B127" s="60"/>
       <c r="C127" s="59"/>
       <c r="D127" s="59"/>
@@ -4364,7 +4364,7 @@
       <c r="I127" s="60"/>
       <c r="J127" s="60"/>
     </row>
-    <row r="128" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B128" s="60"/>
       <c r="C128" s="59"/>
       <c r="D128" s="59"/>
@@ -4375,7 +4375,7 @@
       <c r="I128" s="60"/>
       <c r="J128" s="60"/>
     </row>
-    <row r="129" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B129" s="60"/>
       <c r="C129" s="59"/>
       <c r="D129" s="59"/>
@@ -4386,7 +4386,7 @@
       <c r="I129" s="60"/>
       <c r="J129" s="60"/>
     </row>
-    <row r="130" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B130" s="60"/>
       <c r="C130" s="59"/>
       <c r="D130" s="59"/>
@@ -4397,7 +4397,7 @@
       <c r="I130" s="60"/>
       <c r="J130" s="60"/>
     </row>
-    <row r="131" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B131" s="60"/>
       <c r="C131" s="59"/>
       <c r="D131" s="59"/>
@@ -4408,7 +4408,7 @@
       <c r="I131" s="60"/>
       <c r="J131" s="60"/>
     </row>
-    <row r="132" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B132" s="60"/>
       <c r="C132" s="59"/>
       <c r="D132" s="59"/>
@@ -4419,7 +4419,7 @@
       <c r="I132" s="60"/>
       <c r="J132" s="60"/>
     </row>
-    <row r="133" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B133" s="60"/>
       <c r="C133" s="59"/>
       <c r="D133" s="59"/>
@@ -4430,7 +4430,7 @@
       <c r="I133" s="60"/>
       <c r="J133" s="60"/>
     </row>
-    <row r="134" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B134" s="60"/>
       <c r="C134" s="59"/>
       <c r="D134" s="59"/>
@@ -4441,7 +4441,7 @@
       <c r="I134" s="60"/>
       <c r="J134" s="60"/>
     </row>
-    <row r="135" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B135" s="60"/>
       <c r="C135" s="59"/>
       <c r="D135" s="59"/>
@@ -4452,7 +4452,7 @@
       <c r="I135" s="60"/>
       <c r="J135" s="60"/>
     </row>
-    <row r="136" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B136" s="60"/>
       <c r="C136" s="59"/>
       <c r="D136" s="59"/>
@@ -4463,7 +4463,7 @@
       <c r="I136" s="60"/>
       <c r="J136" s="60"/>
     </row>
-    <row r="137" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B137" s="60"/>
       <c r="C137" s="59"/>
       <c r="D137" s="59"/>
@@ -4474,7 +4474,7 @@
       <c r="I137" s="60"/>
       <c r="J137" s="60"/>
     </row>
-    <row r="138" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B138" s="60"/>
       <c r="C138" s="59"/>
       <c r="D138" s="59"/>
@@ -4485,7 +4485,7 @@
       <c r="I138" s="60"/>
       <c r="J138" s="60"/>
     </row>
-    <row r="139" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B139" s="60"/>
       <c r="C139" s="59"/>
       <c r="D139" s="59"/>
@@ -4496,7 +4496,7 @@
       <c r="I139" s="60"/>
       <c r="J139" s="60"/>
     </row>
-    <row r="140" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B140" s="60"/>
       <c r="C140" s="59"/>
       <c r="D140" s="59"/>
@@ -4507,7 +4507,7 @@
       <c r="I140" s="60"/>
       <c r="J140" s="60"/>
     </row>
-    <row r="141" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B141" s="60"/>
       <c r="C141" s="59"/>
       <c r="D141" s="59"/>
@@ -4518,7 +4518,7 @@
       <c r="I141" s="60"/>
       <c r="J141" s="60"/>
     </row>
-    <row r="142" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B142" s="60"/>
       <c r="C142" s="59"/>
       <c r="D142" s="59"/>
@@ -4529,7 +4529,7 @@
       <c r="I142" s="60"/>
       <c r="J142" s="60"/>
     </row>
-    <row r="143" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B143" s="60"/>
       <c r="C143" s="59"/>
       <c r="D143" s="59"/>
@@ -4540,7 +4540,7 @@
       <c r="I143" s="60"/>
       <c r="J143" s="60"/>
     </row>
-    <row r="144" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B144" s="60"/>
       <c r="C144" s="59"/>
       <c r="D144" s="59"/>
@@ -4551,7 +4551,7 @@
       <c r="I144" s="60"/>
       <c r="J144" s="60"/>
     </row>
-    <row r="145" spans="2:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B145" s="60"/>
       <c r="C145" s="42"/>
       <c r="D145" s="42"/>
@@ -4559,7 +4559,7 @@
       <c r="F145" s="42"/>
       <c r="G145" s="42"/>
     </row>
-    <row r="146" spans="2:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="60"/>
       <c r="C146" s="42"/>
       <c r="D146" s="42"/>
@@ -4567,7 +4567,7 @@
       <c r="F146" s="42"/>
       <c r="G146" s="42"/>
     </row>
-    <row r="147" spans="2:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="60"/>
       <c r="C147" s="42"/>
       <c r="D147" s="42"/>
@@ -4575,7 +4575,7 @@
       <c r="F147" s="42"/>
       <c r="G147" s="42"/>
     </row>
-    <row r="148" spans="2:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B148" s="60"/>
       <c r="C148" s="42"/>
       <c r="D148" s="42"/>
@@ -4583,7 +4583,7 @@
       <c r="F148" s="42"/>
       <c r="G148" s="42"/>
     </row>
-    <row r="149" spans="2:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B149" s="60"/>
       <c r="C149" s="42"/>
       <c r="D149" s="42"/>
@@ -4591,7 +4591,7 @@
       <c r="F149" s="42"/>
       <c r="G149" s="42"/>
     </row>
-    <row r="150" spans="2:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B150" s="60"/>
       <c r="C150" s="42"/>
       <c r="D150" s="42"/>
@@ -4599,7 +4599,7 @@
       <c r="F150" s="42"/>
       <c r="G150" s="42"/>
     </row>
-    <row r="151" spans="2:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B151" s="60"/>
       <c r="C151" s="42"/>
       <c r="D151" s="42"/>
@@ -4607,7 +4607,7 @@
       <c r="F151" s="42"/>
       <c r="G151" s="42"/>
     </row>
-    <row r="152" spans="2:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B152" s="60"/>
       <c r="C152" s="42"/>
       <c r="D152" s="42"/>
@@ -4615,7 +4615,7 @@
       <c r="F152" s="42"/>
       <c r="G152" s="42"/>
     </row>
-    <row r="153" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B153" s="60"/>
       <c r="C153" s="42"/>
       <c r="D153" s="42"/>
@@ -4623,7 +4623,7 @@
       <c r="F153" s="42"/>
       <c r="G153" s="42"/>
     </row>
-    <row r="154" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B154" s="60"/>
       <c r="C154" s="42"/>
       <c r="D154" s="42"/>
@@ -4631,7 +4631,7 @@
       <c r="F154" s="42"/>
       <c r="G154" s="42"/>
     </row>
-    <row r="155" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B155" s="60"/>
       <c r="C155" s="42"/>
       <c r="D155" s="42"/>
@@ -4639,7 +4639,7 @@
       <c r="F155" s="42"/>
       <c r="G155" s="42"/>
     </row>
-    <row r="156" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B156" s="60"/>
       <c r="C156" s="42"/>
       <c r="D156" s="42"/>
@@ -4647,7 +4647,7 @@
       <c r="F156" s="42"/>
       <c r="G156" s="42"/>
     </row>
-    <row r="157" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B157" s="60"/>
       <c r="C157" s="42"/>
       <c r="D157" s="42"/>
@@ -4655,7 +4655,7 @@
       <c r="F157" s="42"/>
       <c r="G157" s="42"/>
     </row>
-    <row r="158" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B158" s="60"/>
       <c r="C158" s="42"/>
       <c r="D158" s="42"/>
@@ -4663,7 +4663,7 @@
       <c r="F158" s="42"/>
       <c r="G158" s="42"/>
     </row>
-    <row r="159" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B159" s="60"/>
       <c r="C159" s="42"/>
       <c r="D159" s="42"/>
@@ -4671,7 +4671,7 @@
       <c r="F159" s="42"/>
       <c r="G159" s="42"/>
     </row>
-    <row r="160" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B160" s="60"/>
       <c r="C160" s="42"/>
       <c r="D160" s="42"/>
@@ -4679,7 +4679,7 @@
       <c r="F160" s="42"/>
       <c r="G160" s="42"/>
     </row>
-    <row r="161" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B161" s="60"/>
       <c r="C161" s="42"/>
       <c r="D161" s="42"/>
@@ -4687,7 +4687,7 @@
       <c r="F161" s="42"/>
       <c r="G161" s="42"/>
     </row>
-    <row r="162" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B162" s="60"/>
       <c r="C162" s="42"/>
       <c r="D162" s="42"/>
@@ -4695,7 +4695,7 @@
       <c r="F162" s="42"/>
       <c r="G162" s="42"/>
     </row>
-    <row r="163" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B163" s="60"/>
       <c r="C163" s="42"/>
       <c r="D163" s="42"/>
@@ -4703,7 +4703,7 @@
       <c r="F163" s="42"/>
       <c r="G163" s="42"/>
     </row>
-    <row r="164" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B164" s="60"/>
       <c r="C164" s="42"/>
       <c r="D164" s="42"/>
@@ -4711,7 +4711,7 @@
       <c r="F164" s="42"/>
       <c r="G164" s="42"/>
     </row>
-    <row r="165" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B165" s="60"/>
       <c r="C165" s="42"/>
       <c r="D165" s="42"/>
@@ -4719,7 +4719,7 @@
       <c r="F165" s="42"/>
       <c r="G165" s="42"/>
     </row>
-    <row r="166" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B166" s="60"/>
       <c r="C166" s="42"/>
       <c r="D166" s="42"/>
@@ -4727,7 +4727,7 @@
       <c r="F166" s="42"/>
       <c r="G166" s="42"/>
     </row>
-    <row r="167" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B167" s="60"/>
       <c r="C167" s="42"/>
       <c r="D167" s="42"/>
@@ -4735,7 +4735,7 @@
       <c r="F167" s="42"/>
       <c r="G167" s="42"/>
     </row>
-    <row r="168" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B168" s="60"/>
       <c r="C168" s="42"/>
       <c r="D168" s="42"/>
@@ -4743,7 +4743,7 @@
       <c r="F168" s="42"/>
       <c r="G168" s="42"/>
     </row>
-    <row r="169" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B169" s="60"/>
       <c r="C169" s="42"/>
       <c r="D169" s="42"/>
@@ -4751,7 +4751,7 @@
       <c r="F169" s="42"/>
       <c r="G169" s="42"/>
     </row>
-    <row r="170" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B170" s="60"/>
       <c r="C170" s="42"/>
       <c r="D170" s="42"/>
@@ -4759,7 +4759,7 @@
       <c r="F170" s="42"/>
       <c r="G170" s="42"/>
     </row>
-    <row r="171" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B171" s="60"/>
       <c r="C171" s="42"/>
       <c r="D171" s="42"/>
@@ -4767,7 +4767,7 @@
       <c r="F171" s="42"/>
       <c r="G171" s="42"/>
     </row>
-    <row r="172" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B172" s="60"/>
       <c r="C172" s="42"/>
       <c r="D172" s="42"/>
@@ -4775,7 +4775,7 @@
       <c r="F172" s="42"/>
       <c r="G172" s="42"/>
     </row>
-    <row r="173" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B173" s="60"/>
       <c r="C173" s="42"/>
       <c r="D173" s="42"/>
@@ -4783,7 +4783,7 @@
       <c r="F173" s="42"/>
       <c r="G173" s="42"/>
     </row>
-    <row r="174" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B174" s="60"/>
       <c r="C174" s="42"/>
       <c r="D174" s="42"/>
@@ -4791,7 +4791,7 @@
       <c r="F174" s="42"/>
       <c r="G174" s="42"/>
     </row>
-    <row r="175" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B175" s="60"/>
       <c r="C175" s="42"/>
       <c r="D175" s="42"/>
@@ -4799,7 +4799,7 @@
       <c r="F175" s="42"/>
       <c r="G175" s="42"/>
     </row>
-    <row r="176" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B176" s="60"/>
       <c r="C176" s="42"/>
       <c r="D176" s="42"/>
@@ -4807,7 +4807,7 @@
       <c r="F176" s="42"/>
       <c r="G176" s="42"/>
     </row>
-    <row r="177" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B177" s="60"/>
       <c r="C177" s="42"/>
       <c r="D177" s="42"/>
@@ -4815,7 +4815,7 @@
       <c r="F177" s="42"/>
       <c r="G177" s="42"/>
     </row>
-    <row r="178" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B178" s="60"/>
       <c r="C178" s="42"/>
       <c r="D178" s="42"/>
@@ -4823,7 +4823,7 @@
       <c r="F178" s="42"/>
       <c r="G178" s="42"/>
     </row>
-    <row r="179" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B179" s="60"/>
       <c r="C179" s="42"/>
       <c r="D179" s="42"/>
@@ -4831,7 +4831,7 @@
       <c r="F179" s="42"/>
       <c r="G179" s="42"/>
     </row>
-    <row r="180" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B180" s="60"/>
       <c r="C180" s="42"/>
       <c r="D180" s="42"/>
@@ -4839,7 +4839,7 @@
       <c r="F180" s="42"/>
       <c r="G180" s="42"/>
     </row>
-    <row r="181" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B181" s="60"/>
       <c r="C181" s="42"/>
       <c r="D181" s="42"/>
@@ -4847,7 +4847,7 @@
       <c r="F181" s="42"/>
       <c r="G181" s="42"/>
     </row>
-    <row r="182" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B182" s="60"/>
       <c r="C182" s="42"/>
       <c r="D182" s="42"/>
@@ -4855,7 +4855,7 @@
       <c r="F182" s="42"/>
       <c r="G182" s="42"/>
     </row>
-    <row r="183" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B183" s="60"/>
       <c r="C183" s="42"/>
       <c r="D183" s="42"/>
@@ -4863,7 +4863,7 @@
       <c r="F183" s="42"/>
       <c r="G183" s="42"/>
     </row>
-    <row r="184" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B184" s="60"/>
       <c r="C184" s="42"/>
       <c r="D184" s="42"/>
@@ -4871,7 +4871,7 @@
       <c r="F184" s="42"/>
       <c r="G184" s="42"/>
     </row>
-    <row r="185" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B185" s="60"/>
       <c r="C185" s="42"/>
       <c r="D185" s="42"/>
@@ -4879,7 +4879,7 @@
       <c r="F185" s="42"/>
       <c r="G185" s="42"/>
     </row>
-    <row r="186" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B186" s="60"/>
       <c r="C186" s="42"/>
       <c r="D186" s="42"/>
@@ -4887,7 +4887,7 @@
       <c r="F186" s="42"/>
       <c r="G186" s="42"/>
     </row>
-    <row r="187" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B187" s="60"/>
       <c r="C187" s="42"/>
       <c r="D187" s="42"/>
@@ -4895,7 +4895,7 @@
       <c r="F187" s="42"/>
       <c r="G187" s="42"/>
     </row>
-    <row r="188" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B188" s="60"/>
       <c r="C188" s="42"/>
       <c r="D188" s="42"/>
@@ -4903,7 +4903,7 @@
       <c r="F188" s="42"/>
       <c r="G188" s="42"/>
     </row>
-    <row r="189" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B189" s="60"/>
       <c r="C189" s="42"/>
       <c r="D189" s="42"/>
@@ -4911,7 +4911,7 @@
       <c r="F189" s="42"/>
       <c r="G189" s="42"/>
     </row>
-    <row r="190" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B190" s="60"/>
       <c r="C190" s="42"/>
       <c r="D190" s="42"/>
@@ -4919,7 +4919,7 @@
       <c r="F190" s="42"/>
       <c r="G190" s="42"/>
     </row>
-    <row r="191" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B191" s="60"/>
       <c r="C191" s="42"/>
       <c r="D191" s="42"/>
@@ -4927,7 +4927,7 @@
       <c r="F191" s="42"/>
       <c r="G191" s="42"/>
     </row>
-    <row r="192" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B192" s="60"/>
       <c r="C192" s="42"/>
       <c r="D192" s="42"/>
@@ -4935,7 +4935,7 @@
       <c r="F192" s="42"/>
       <c r="G192" s="42"/>
     </row>
-    <row r="193" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B193" s="60"/>
       <c r="C193" s="42"/>
       <c r="D193" s="42"/>
@@ -4943,1062 +4943,1065 @@
       <c r="F193" s="42"/>
       <c r="G193" s="42"/>
     </row>
-    <row r="194" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C194" s="42"/>
       <c r="D194" s="42"/>
       <c r="E194" s="42"/>
       <c r="F194" s="42"/>
       <c r="G194" s="42"/>
     </row>
-    <row r="195" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C195" s="42"/>
       <c r="D195" s="42"/>
       <c r="E195" s="42"/>
       <c r="F195" s="42"/>
       <c r="G195" s="42"/>
     </row>
-    <row r="196" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C196" s="42"/>
       <c r="D196" s="42"/>
       <c r="E196" s="42"/>
       <c r="F196" s="42"/>
       <c r="G196" s="42"/>
     </row>
-    <row r="197" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C197" s="42"/>
       <c r="D197" s="42"/>
       <c r="E197" s="42"/>
       <c r="F197" s="42"/>
       <c r="G197" s="42"/>
     </row>
-    <row r="198" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C198" s="42"/>
       <c r="D198" s="42"/>
       <c r="E198" s="42"/>
       <c r="F198" s="42"/>
       <c r="G198" s="42"/>
     </row>
-    <row r="199" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C199" s="42"/>
       <c r="D199" s="42"/>
       <c r="E199" s="42"/>
       <c r="F199" s="42"/>
       <c r="G199" s="42"/>
     </row>
-    <row r="200" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C200" s="42"/>
       <c r="D200" s="42"/>
       <c r="E200" s="42"/>
       <c r="F200" s="42"/>
       <c r="G200" s="42"/>
     </row>
-    <row r="201" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C201" s="42"/>
       <c r="D201" s="42"/>
       <c r="E201" s="42"/>
       <c r="F201" s="42"/>
       <c r="G201" s="42"/>
     </row>
-    <row r="202" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C202" s="42"/>
       <c r="D202" s="42"/>
       <c r="E202" s="42"/>
       <c r="F202" s="42"/>
       <c r="G202" s="42"/>
     </row>
-    <row r="203" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C203" s="42"/>
       <c r="D203" s="42"/>
       <c r="E203" s="42"/>
       <c r="F203" s="42"/>
       <c r="G203" s="42"/>
     </row>
-    <row r="204" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C204" s="42"/>
       <c r="D204" s="42"/>
       <c r="E204" s="42"/>
       <c r="F204" s="42"/>
       <c r="G204" s="42"/>
     </row>
-    <row r="205" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C205" s="42"/>
       <c r="D205" s="42"/>
       <c r="E205" s="42"/>
       <c r="F205" s="42"/>
       <c r="G205" s="42"/>
     </row>
-    <row r="206" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C206" s="42"/>
       <c r="D206" s="42"/>
       <c r="E206" s="42"/>
       <c r="F206" s="42"/>
       <c r="G206" s="42"/>
     </row>
-    <row r="207" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C207" s="42"/>
       <c r="D207" s="42"/>
       <c r="E207" s="42"/>
       <c r="F207" s="42"/>
       <c r="G207" s="42"/>
     </row>
-    <row r="208" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C208" s="42"/>
       <c r="D208" s="42"/>
       <c r="E208" s="42"/>
       <c r="F208" s="42"/>
       <c r="G208" s="42"/>
     </row>
-    <row r="209" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C209" s="42"/>
       <c r="D209" s="42"/>
       <c r="E209" s="42"/>
       <c r="F209" s="42"/>
       <c r="G209" s="42"/>
     </row>
-    <row r="210" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C210" s="42"/>
       <c r="D210" s="42"/>
       <c r="E210" s="42"/>
       <c r="F210" s="42"/>
       <c r="G210" s="42"/>
     </row>
-    <row r="211" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C211" s="42"/>
       <c r="D211" s="42"/>
       <c r="E211" s="42"/>
       <c r="F211" s="42"/>
       <c r="G211" s="42"/>
     </row>
-    <row r="212" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C212" s="42"/>
       <c r="D212" s="42"/>
       <c r="E212" s="42"/>
       <c r="F212" s="42"/>
       <c r="G212" s="42"/>
     </row>
-    <row r="213" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C213" s="42"/>
       <c r="D213" s="42"/>
       <c r="E213" s="42"/>
       <c r="F213" s="42"/>
       <c r="G213" s="42"/>
     </row>
-    <row r="214" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C214" s="42"/>
       <c r="D214" s="42"/>
       <c r="E214" s="42"/>
       <c r="F214" s="42"/>
       <c r="G214" s="42"/>
     </row>
-    <row r="215" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C215" s="42"/>
       <c r="D215" s="42"/>
       <c r="E215" s="42"/>
       <c r="F215" s="42"/>
       <c r="G215" s="42"/>
     </row>
-    <row r="216" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C216" s="42"/>
       <c r="D216" s="42"/>
       <c r="E216" s="42"/>
       <c r="F216" s="42"/>
       <c r="G216" s="42"/>
     </row>
-    <row r="217" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C217" s="42"/>
       <c r="D217" s="42"/>
       <c r="E217" s="42"/>
       <c r="F217" s="42"/>
       <c r="G217" s="42"/>
     </row>
-    <row r="218" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C218" s="42"/>
       <c r="D218" s="42"/>
       <c r="E218" s="42"/>
       <c r="F218" s="42"/>
       <c r="G218" s="42"/>
     </row>
-    <row r="219" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C219" s="42"/>
       <c r="D219" s="42"/>
       <c r="E219" s="42"/>
       <c r="F219" s="42"/>
       <c r="G219" s="42"/>
     </row>
-    <row r="220" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C220" s="42"/>
       <c r="D220" s="42"/>
       <c r="E220" s="42"/>
       <c r="F220" s="42"/>
       <c r="G220" s="42"/>
     </row>
-    <row r="221" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C221" s="42"/>
       <c r="D221" s="42"/>
       <c r="E221" s="42"/>
       <c r="F221" s="42"/>
       <c r="G221" s="42"/>
     </row>
-    <row r="222" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C222" s="42"/>
       <c r="D222" s="42"/>
       <c r="E222" s="42"/>
       <c r="F222" s="42"/>
       <c r="G222" s="42"/>
     </row>
-    <row r="223" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C223" s="42"/>
       <c r="D223" s="42"/>
       <c r="E223" s="42"/>
       <c r="F223" s="42"/>
       <c r="G223" s="42"/>
     </row>
-    <row r="224" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C224" s="42"/>
       <c r="D224" s="42"/>
       <c r="E224" s="42"/>
       <c r="F224" s="42"/>
       <c r="G224" s="42"/>
     </row>
-    <row r="225" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C225" s="42"/>
       <c r="D225" s="42"/>
       <c r="E225" s="42"/>
       <c r="F225" s="42"/>
       <c r="G225" s="42"/>
     </row>
-    <row r="226" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C226" s="42"/>
       <c r="D226" s="42"/>
       <c r="E226" s="42"/>
       <c r="F226" s="42"/>
       <c r="G226" s="42"/>
     </row>
-    <row r="227" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C227" s="42"/>
       <c r="D227" s="42"/>
       <c r="E227" s="42"/>
       <c r="F227" s="42"/>
       <c r="G227" s="42"/>
     </row>
-    <row r="228" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C228" s="42"/>
       <c r="D228" s="42"/>
       <c r="E228" s="42"/>
       <c r="F228" s="42"/>
       <c r="G228" s="42"/>
     </row>
-    <row r="229" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C229" s="42"/>
       <c r="D229" s="42"/>
       <c r="E229" s="42"/>
       <c r="F229" s="42"/>
       <c r="G229" s="42"/>
     </row>
-    <row r="230" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C230" s="42"/>
       <c r="D230" s="42"/>
       <c r="E230" s="42"/>
       <c r="F230" s="42"/>
       <c r="G230" s="42"/>
     </row>
-    <row r="231" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C231" s="42"/>
       <c r="D231" s="42"/>
       <c r="E231" s="42"/>
       <c r="F231" s="42"/>
       <c r="G231" s="42"/>
     </row>
-    <row r="232" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C232" s="42"/>
       <c r="D232" s="42"/>
       <c r="E232" s="42"/>
       <c r="F232" s="42"/>
       <c r="G232" s="42"/>
     </row>
-    <row r="233" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C233" s="42"/>
       <c r="D233" s="42"/>
       <c r="E233" s="42"/>
       <c r="F233" s="42"/>
       <c r="G233" s="42"/>
     </row>
-    <row r="234" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C234" s="42"/>
       <c r="D234" s="42"/>
       <c r="E234" s="42"/>
       <c r="F234" s="42"/>
       <c r="G234" s="42"/>
     </row>
-    <row r="235" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C235" s="42"/>
       <c r="D235" s="42"/>
       <c r="E235" s="42"/>
       <c r="F235" s="42"/>
       <c r="G235" s="42"/>
     </row>
-    <row r="236" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C236" s="42"/>
       <c r="D236" s="42"/>
       <c r="E236" s="42"/>
       <c r="F236" s="42"/>
       <c r="G236" s="42"/>
     </row>
-    <row r="237" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C237" s="42"/>
       <c r="D237" s="42"/>
       <c r="E237" s="42"/>
       <c r="F237" s="42"/>
       <c r="G237" s="42"/>
     </row>
-    <row r="238" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C238" s="42"/>
       <c r="D238" s="42"/>
       <c r="E238" s="42"/>
       <c r="F238" s="42"/>
       <c r="G238" s="42"/>
     </row>
-    <row r="239" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C239" s="42"/>
       <c r="D239" s="42"/>
       <c r="E239" s="42"/>
       <c r="F239" s="42"/>
       <c r="G239" s="42"/>
     </row>
-    <row r="240" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C240" s="42"/>
       <c r="D240" s="42"/>
       <c r="E240" s="42"/>
       <c r="F240" s="42"/>
       <c r="G240" s="42"/>
     </row>
-    <row r="241" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C241" s="42"/>
       <c r="D241" s="42"/>
       <c r="E241" s="42"/>
       <c r="F241" s="42"/>
       <c r="G241" s="42"/>
     </row>
-    <row r="242" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C242" s="42"/>
       <c r="D242" s="42"/>
       <c r="E242" s="42"/>
       <c r="F242" s="42"/>
       <c r="G242" s="42"/>
     </row>
-    <row r="243" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C243" s="42"/>
       <c r="D243" s="42"/>
       <c r="E243" s="42"/>
       <c r="F243" s="42"/>
       <c r="G243" s="42"/>
     </row>
-    <row r="244" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C244" s="42"/>
       <c r="D244" s="42"/>
       <c r="E244" s="42"/>
       <c r="F244" s="42"/>
       <c r="G244" s="42"/>
     </row>
-    <row r="245" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C245" s="42"/>
       <c r="D245" s="42"/>
       <c r="E245" s="42"/>
       <c r="F245" s="42"/>
       <c r="G245" s="42"/>
     </row>
-    <row r="246" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C246" s="42"/>
       <c r="D246" s="42"/>
       <c r="E246" s="42"/>
       <c r="F246" s="42"/>
       <c r="G246" s="42"/>
     </row>
-    <row r="247" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C247" s="42"/>
       <c r="D247" s="42"/>
       <c r="E247" s="42"/>
       <c r="F247" s="42"/>
       <c r="G247" s="42"/>
     </row>
-    <row r="248" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C248" s="42"/>
       <c r="D248" s="42"/>
       <c r="E248" s="42"/>
       <c r="F248" s="42"/>
       <c r="G248" s="42"/>
     </row>
-    <row r="249" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C249" s="42"/>
       <c r="D249" s="42"/>
       <c r="E249" s="42"/>
       <c r="F249" s="42"/>
       <c r="G249" s="42"/>
     </row>
-    <row r="250" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C250" s="42"/>
       <c r="D250" s="42"/>
       <c r="E250" s="42"/>
       <c r="F250" s="42"/>
       <c r="G250" s="42"/>
     </row>
-    <row r="251" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C251" s="42"/>
       <c r="D251" s="42"/>
       <c r="E251" s="42"/>
       <c r="F251" s="42"/>
       <c r="G251" s="42"/>
     </row>
-    <row r="252" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C252" s="42"/>
       <c r="D252" s="42"/>
       <c r="E252" s="42"/>
       <c r="F252" s="42"/>
       <c r="G252" s="42"/>
     </row>
-    <row r="253" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C253" s="42"/>
       <c r="D253" s="42"/>
       <c r="E253" s="42"/>
       <c r="F253" s="42"/>
       <c r="G253" s="42"/>
     </row>
-    <row r="254" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C254" s="42"/>
       <c r="D254" s="42"/>
       <c r="E254" s="42"/>
       <c r="F254" s="42"/>
       <c r="G254" s="42"/>
     </row>
-    <row r="255" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C255" s="42"/>
       <c r="D255" s="42"/>
       <c r="E255" s="42"/>
       <c r="F255" s="42"/>
       <c r="G255" s="42"/>
     </row>
-    <row r="256" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C256" s="42"/>
       <c r="D256" s="42"/>
       <c r="E256" s="42"/>
       <c r="F256" s="42"/>
       <c r="G256" s="42"/>
     </row>
-    <row r="257" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C257" s="42"/>
       <c r="D257" s="42"/>
       <c r="E257" s="42"/>
       <c r="F257" s="42"/>
       <c r="G257" s="42"/>
     </row>
-    <row r="258" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C258" s="42"/>
       <c r="D258" s="42"/>
       <c r="E258" s="42"/>
       <c r="F258" s="42"/>
       <c r="G258" s="42"/>
     </row>
-    <row r="259" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C259" s="42"/>
       <c r="D259" s="42"/>
       <c r="E259" s="42"/>
       <c r="F259" s="42"/>
       <c r="G259" s="42"/>
     </row>
-    <row r="260" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C260" s="42"/>
       <c r="D260" s="42"/>
       <c r="E260" s="42"/>
       <c r="F260" s="42"/>
       <c r="G260" s="42"/>
     </row>
-    <row r="261" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C261" s="42"/>
       <c r="D261" s="42"/>
       <c r="E261" s="42"/>
       <c r="F261" s="42"/>
       <c r="G261" s="42"/>
     </row>
-    <row r="262" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C262" s="42"/>
       <c r="D262" s="42"/>
       <c r="E262" s="42"/>
       <c r="F262" s="42"/>
       <c r="G262" s="42"/>
     </row>
-    <row r="263" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C263" s="42"/>
       <c r="D263" s="42"/>
       <c r="E263" s="42"/>
       <c r="F263" s="42"/>
       <c r="G263" s="42"/>
     </row>
-    <row r="264" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C264" s="42"/>
       <c r="D264" s="42"/>
       <c r="E264" s="42"/>
       <c r="F264" s="42"/>
       <c r="G264" s="42"/>
     </row>
-    <row r="265" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C265" s="42"/>
       <c r="D265" s="42"/>
       <c r="E265" s="42"/>
       <c r="F265" s="42"/>
       <c r="G265" s="42"/>
     </row>
-    <row r="266" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C266" s="42"/>
       <c r="D266" s="42"/>
       <c r="E266" s="42"/>
       <c r="F266" s="42"/>
       <c r="G266" s="42"/>
     </row>
-    <row r="267" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C267" s="42"/>
       <c r="D267" s="42"/>
       <c r="E267" s="42"/>
       <c r="F267" s="42"/>
       <c r="G267" s="42"/>
     </row>
-    <row r="268" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C268" s="42"/>
       <c r="D268" s="42"/>
       <c r="E268" s="42"/>
       <c r="F268" s="42"/>
       <c r="G268" s="42"/>
     </row>
-    <row r="269" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C269" s="42"/>
       <c r="D269" s="42"/>
       <c r="E269" s="42"/>
       <c r="F269" s="42"/>
       <c r="G269" s="42"/>
     </row>
-    <row r="270" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C270" s="42"/>
       <c r="D270" s="42"/>
       <c r="E270" s="42"/>
       <c r="F270" s="42"/>
       <c r="G270" s="42"/>
     </row>
-    <row r="271" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C271" s="42"/>
       <c r="D271" s="42"/>
       <c r="E271" s="42"/>
       <c r="F271" s="42"/>
       <c r="G271" s="42"/>
     </row>
-    <row r="272" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C272" s="42"/>
       <c r="D272" s="42"/>
       <c r="E272" s="42"/>
       <c r="F272" s="42"/>
       <c r="G272" s="42"/>
     </row>
-    <row r="273" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C273" s="42"/>
       <c r="D273" s="42"/>
       <c r="E273" s="42"/>
       <c r="F273" s="42"/>
       <c r="G273" s="42"/>
     </row>
-    <row r="274" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C274" s="42"/>
       <c r="D274" s="42"/>
       <c r="E274" s="42"/>
       <c r="F274" s="42"/>
       <c r="G274" s="42"/>
     </row>
-    <row r="275" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C275" s="42"/>
       <c r="D275" s="42"/>
       <c r="E275" s="42"/>
       <c r="F275" s="42"/>
       <c r="G275" s="42"/>
     </row>
-    <row r="276" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C276" s="42"/>
       <c r="D276" s="42"/>
       <c r="E276" s="42"/>
       <c r="F276" s="42"/>
       <c r="G276" s="42"/>
     </row>
-    <row r="277" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C277" s="42"/>
       <c r="D277" s="42"/>
       <c r="E277" s="42"/>
       <c r="F277" s="42"/>
       <c r="G277" s="42"/>
     </row>
-    <row r="278" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C278" s="42"/>
       <c r="D278" s="42"/>
       <c r="E278" s="42"/>
       <c r="F278" s="42"/>
       <c r="G278" s="42"/>
     </row>
-    <row r="279" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C279" s="42"/>
       <c r="D279" s="42"/>
       <c r="E279" s="42"/>
       <c r="F279" s="42"/>
       <c r="G279" s="42"/>
     </row>
-    <row r="280" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C280" s="42"/>
       <c r="D280" s="42"/>
       <c r="E280" s="42"/>
       <c r="F280" s="42"/>
       <c r="G280" s="42"/>
     </row>
-    <row r="281" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C281" s="42"/>
       <c r="D281" s="42"/>
       <c r="E281" s="42"/>
       <c r="F281" s="42"/>
       <c r="G281" s="42"/>
     </row>
-    <row r="282" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C282" s="42"/>
       <c r="D282" s="42"/>
       <c r="E282" s="42"/>
       <c r="F282" s="42"/>
       <c r="G282" s="42"/>
     </row>
-    <row r="283" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C283" s="42"/>
       <c r="D283" s="42"/>
       <c r="E283" s="42"/>
       <c r="F283" s="42"/>
       <c r="G283" s="42"/>
     </row>
-    <row r="284" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C284" s="42"/>
       <c r="D284" s="42"/>
       <c r="E284" s="42"/>
       <c r="F284" s="42"/>
       <c r="G284" s="42"/>
     </row>
-    <row r="285" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C285" s="42"/>
       <c r="D285" s="42"/>
       <c r="E285" s="42"/>
       <c r="F285" s="42"/>
       <c r="G285" s="42"/>
     </row>
-    <row r="286" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C286" s="42"/>
       <c r="D286" s="42"/>
       <c r="E286" s="42"/>
       <c r="F286" s="42"/>
       <c r="G286" s="42"/>
     </row>
-    <row r="287" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C287" s="42"/>
       <c r="D287" s="42"/>
       <c r="E287" s="42"/>
       <c r="F287" s="42"/>
       <c r="G287" s="42"/>
     </row>
-    <row r="288" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C288" s="42"/>
       <c r="D288" s="42"/>
       <c r="E288" s="42"/>
       <c r="F288" s="42"/>
       <c r="G288" s="42"/>
     </row>
-    <row r="289" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C289" s="42"/>
       <c r="D289" s="42"/>
       <c r="E289" s="42"/>
       <c r="F289" s="42"/>
       <c r="G289" s="42"/>
     </row>
-    <row r="290" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C290" s="42"/>
       <c r="D290" s="42"/>
       <c r="E290" s="42"/>
       <c r="F290" s="42"/>
       <c r="G290" s="42"/>
     </row>
-    <row r="291" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C291" s="42"/>
       <c r="D291" s="42"/>
       <c r="E291" s="42"/>
       <c r="F291" s="42"/>
       <c r="G291" s="42"/>
     </row>
-    <row r="292" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C292" s="42"/>
       <c r="D292" s="42"/>
       <c r="E292" s="42"/>
       <c r="F292" s="42"/>
       <c r="G292" s="42"/>
     </row>
-    <row r="293" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C293" s="42"/>
       <c r="D293" s="42"/>
       <c r="E293" s="42"/>
       <c r="F293" s="42"/>
       <c r="G293" s="42"/>
     </row>
-    <row r="294" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C294" s="42"/>
       <c r="D294" s="42"/>
       <c r="E294" s="42"/>
       <c r="F294" s="42"/>
       <c r="G294" s="42"/>
     </row>
-    <row r="295" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C295" s="42"/>
       <c r="D295" s="42"/>
       <c r="E295" s="42"/>
       <c r="F295" s="42"/>
       <c r="G295" s="42"/>
     </row>
-    <row r="296" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C296" s="42"/>
       <c r="D296" s="42"/>
       <c r="E296" s="42"/>
       <c r="F296" s="42"/>
       <c r="G296" s="42"/>
     </row>
-    <row r="297" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C297" s="42"/>
       <c r="D297" s="42"/>
       <c r="E297" s="42"/>
       <c r="F297" s="42"/>
       <c r="G297" s="42"/>
     </row>
-    <row r="298" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C298" s="42"/>
       <c r="D298" s="42"/>
       <c r="E298" s="42"/>
       <c r="F298" s="42"/>
       <c r="G298" s="42"/>
     </row>
-    <row r="299" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C299" s="42"/>
       <c r="D299" s="42"/>
       <c r="E299" s="42"/>
       <c r="F299" s="42"/>
       <c r="G299" s="42"/>
     </row>
-    <row r="300" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C300" s="42"/>
       <c r="D300" s="42"/>
       <c r="E300" s="42"/>
       <c r="F300" s="42"/>
       <c r="G300" s="42"/>
     </row>
-    <row r="301" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C301" s="42"/>
       <c r="D301" s="42"/>
       <c r="E301" s="42"/>
       <c r="F301" s="42"/>
       <c r="G301" s="42"/>
     </row>
-    <row r="302" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C302" s="42"/>
       <c r="D302" s="42"/>
       <c r="E302" s="42"/>
       <c r="F302" s="42"/>
       <c r="G302" s="42"/>
     </row>
-    <row r="303" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C303" s="42"/>
       <c r="D303" s="42"/>
       <c r="E303" s="42"/>
       <c r="F303" s="42"/>
       <c r="G303" s="42"/>
     </row>
-    <row r="304" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C304" s="42"/>
       <c r="D304" s="42"/>
       <c r="E304" s="42"/>
       <c r="F304" s="42"/>
       <c r="G304" s="42"/>
     </row>
-    <row r="305" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C305" s="42"/>
       <c r="D305" s="42"/>
       <c r="E305" s="42"/>
       <c r="F305" s="42"/>
       <c r="G305" s="42"/>
     </row>
-    <row r="306" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C306" s="42"/>
       <c r="D306" s="42"/>
       <c r="E306" s="42"/>
       <c r="F306" s="42"/>
       <c r="G306" s="42"/>
     </row>
-    <row r="307" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C307" s="42"/>
       <c r="D307" s="42"/>
       <c r="E307" s="42"/>
       <c r="F307" s="42"/>
       <c r="G307" s="42"/>
     </row>
-    <row r="308" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C308" s="42"/>
       <c r="D308" s="42"/>
       <c r="E308" s="42"/>
       <c r="F308" s="42"/>
       <c r="G308" s="42"/>
     </row>
-    <row r="309" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C309" s="42"/>
       <c r="D309" s="42"/>
       <c r="E309" s="42"/>
       <c r="F309" s="42"/>
       <c r="G309" s="42"/>
     </row>
-    <row r="310" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C310" s="42"/>
       <c r="D310" s="42"/>
       <c r="E310" s="42"/>
       <c r="F310" s="42"/>
       <c r="G310" s="42"/>
     </row>
-    <row r="311" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C311" s="42"/>
       <c r="D311" s="42"/>
       <c r="E311" s="42"/>
       <c r="F311" s="42"/>
       <c r="G311" s="42"/>
     </row>
-    <row r="312" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C312" s="42"/>
       <c r="D312" s="42"/>
       <c r="E312" s="42"/>
       <c r="F312" s="42"/>
       <c r="G312" s="42"/>
     </row>
-    <row r="313" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C313" s="42"/>
       <c r="D313" s="42"/>
       <c r="E313" s="42"/>
       <c r="F313" s="42"/>
       <c r="G313" s="42"/>
     </row>
-    <row r="314" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C314" s="42"/>
       <c r="D314" s="42"/>
       <c r="E314" s="42"/>
       <c r="F314" s="42"/>
       <c r="G314" s="42"/>
     </row>
-    <row r="315" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C315" s="42"/>
       <c r="D315" s="42"/>
       <c r="E315" s="42"/>
       <c r="F315" s="42"/>
       <c r="G315" s="42"/>
     </row>
-    <row r="316" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C316" s="42"/>
       <c r="D316" s="42"/>
       <c r="E316" s="42"/>
       <c r="F316" s="42"/>
       <c r="G316" s="42"/>
     </row>
-    <row r="317" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C317" s="42"/>
       <c r="D317" s="42"/>
       <c r="E317" s="42"/>
       <c r="F317" s="42"/>
       <c r="G317" s="42"/>
     </row>
-    <row r="318" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C318" s="42"/>
       <c r="D318" s="42"/>
       <c r="E318" s="42"/>
       <c r="F318" s="42"/>
       <c r="G318" s="42"/>
     </row>
-    <row r="319" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C319" s="42"/>
       <c r="D319" s="42"/>
       <c r="E319" s="42"/>
       <c r="F319" s="42"/>
       <c r="G319" s="42"/>
     </row>
-    <row r="320" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C320" s="42"/>
       <c r="D320" s="42"/>
       <c r="E320" s="42"/>
       <c r="F320" s="42"/>
       <c r="G320" s="42"/>
     </row>
-    <row r="321" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C321" s="42"/>
       <c r="D321" s="42"/>
       <c r="E321" s="42"/>
       <c r="F321" s="42"/>
       <c r="G321" s="42"/>
     </row>
-    <row r="322" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C322" s="42"/>
       <c r="D322" s="42"/>
       <c r="E322" s="42"/>
       <c r="F322" s="42"/>
       <c r="G322" s="42"/>
     </row>
-    <row r="323" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C323" s="42"/>
       <c r="D323" s="42"/>
       <c r="E323" s="42"/>
       <c r="F323" s="42"/>
       <c r="G323" s="42"/>
     </row>
-    <row r="324" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C324" s="42"/>
       <c r="D324" s="42"/>
       <c r="E324" s="42"/>
       <c r="F324" s="42"/>
       <c r="G324" s="42"/>
     </row>
-    <row r="325" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C325" s="42"/>
       <c r="D325" s="42"/>
       <c r="E325" s="42"/>
       <c r="F325" s="42"/>
       <c r="G325" s="42"/>
     </row>
-    <row r="326" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C326" s="42"/>
       <c r="D326" s="42"/>
       <c r="E326" s="42"/>
       <c r="F326" s="42"/>
       <c r="G326" s="42"/>
     </row>
-    <row r="327" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C327" s="42"/>
       <c r="D327" s="42"/>
       <c r="E327" s="42"/>
       <c r="F327" s="42"/>
       <c r="G327" s="42"/>
     </row>
-    <row r="328" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C328" s="42"/>
       <c r="D328" s="42"/>
       <c r="E328" s="42"/>
       <c r="F328" s="42"/>
       <c r="G328" s="42"/>
     </row>
-    <row r="329" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C329" s="42"/>
       <c r="D329" s="42"/>
       <c r="E329" s="42"/>
       <c r="F329" s="42"/>
       <c r="G329" s="42"/>
     </row>
-    <row r="330" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C330" s="42"/>
       <c r="D330" s="42"/>
       <c r="E330" s="42"/>
       <c r="F330" s="42"/>
       <c r="G330" s="42"/>
     </row>
-    <row r="331" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C331" s="42"/>
       <c r="D331" s="42"/>
       <c r="E331" s="42"/>
       <c r="F331" s="42"/>
       <c r="G331" s="42"/>
     </row>
-    <row r="332" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C332" s="42"/>
       <c r="D332" s="42"/>
       <c r="E332" s="42"/>
       <c r="F332" s="42"/>
       <c r="G332" s="42"/>
     </row>
-    <row r="333" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C333" s="42"/>
       <c r="D333" s="42"/>
       <c r="E333" s="42"/>
       <c r="F333" s="42"/>
       <c r="G333" s="42"/>
     </row>
-    <row r="334" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C334" s="42"/>
       <c r="D334" s="42"/>
       <c r="E334" s="42"/>
       <c r="F334" s="42"/>
       <c r="G334" s="42"/>
     </row>
-    <row r="335" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C335" s="42"/>
       <c r="D335" s="42"/>
       <c r="E335" s="42"/>
       <c r="F335" s="42"/>
       <c r="G335" s="42"/>
     </row>
-    <row r="336" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="3:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C336" s="42"/>
       <c r="D336" s="42"/>
       <c r="E336" s="42"/>
       <c r="F336" s="42"/>
       <c r="G336" s="42"/>
     </row>
-    <row r="337" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C337" s="42"/>
       <c r="D337" s="42"/>
       <c r="E337" s="42"/>
       <c r="F337" s="42"/>
       <c r="G337" s="42"/>
     </row>
-    <row r="338" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C338" s="42"/>
       <c r="D338" s="42"/>
       <c r="E338" s="42"/>
       <c r="F338" s="42"/>
       <c r="G338" s="42"/>
     </row>
-    <row r="339" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C339" s="42"/>
       <c r="D339" s="42"/>
       <c r="E339" s="42"/>
       <c r="F339" s="42"/>
       <c r="G339" s="42"/>
     </row>
-    <row r="340" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C340" s="42"/>
       <c r="D340" s="42"/>
       <c r="E340" s="42"/>
       <c r="F340" s="42"/>
       <c r="G340" s="42"/>
     </row>
-    <row r="341" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C341" s="42"/>
       <c r="D341" s="42"/>
       <c r="E341" s="42"/>
       <c r="F341" s="42"/>
       <c r="G341" s="42"/>
     </row>
-    <row r="342" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="3:11" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C342" s="42"/>
       <c r="D342" s="42"/>
       <c r="E342" s="42"/>
       <c r="F342" s="42"/>
       <c r="G342" s="42"/>
     </row>
-    <row r="343" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="3:11" x14ac:dyDescent="0.35">
       <c r="K343" s="29"/>
     </row>
-    <row r="344" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="3:11" x14ac:dyDescent="0.35">
       <c r="K344" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A77:J77"/>
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
     <mergeCell ref="A74:J74"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -6011,14 +6014,11 @@
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="B58:J58"/>
     <mergeCell ref="A73:J73"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A80:J80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6027,37 +6027,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84552D5A-93F7-463A-891D-22594B68A285}">
   <dimension ref="A1:L376"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" customWidth="1"/>
-    <col min="4" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="42.85546875" customWidth="1"/>
+    <col min="1" max="1" width="36.7265625" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" customWidth="1"/>
+    <col min="4" max="5" width="3.7265625" customWidth="1"/>
+    <col min="6" max="6" width="4.26953125" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.7265625" customWidth="1"/>
+    <col min="10" max="10" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="184"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="237" t="s">
-        <v>266</v>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="186" t="s">
+        <v>264</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="185"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I3" s="3"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.4">
       <c r="A4" s="61" t="s">
         <v>76</v>
       </c>
@@ -6071,7 +6071,7 @@
       <c r="I4" s="62"/>
       <c r="J4" s="62"/>
     </row>
-    <row r="5" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -6083,12 +6083,12 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="B6" s="247" t="s">
-        <v>267</v>
+        <v>270</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>265</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -6101,12 +6101,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="248" t="s">
-        <v>258</v>
+      <c r="B7" s="188" t="s">
+        <v>269</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -6117,11 +6117,11 @@
       <c r="I7" s="15"/>
       <c r="J7" s="13"/>
     </row>
-    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="246" t="s">
+      <c r="B8" s="191" t="s">
         <v>79</v>
       </c>
       <c r="C8" s="15"/>
@@ -6133,12 +6133,12 @@
       <c r="I8" s="15"/>
       <c r="J8" s="13"/>
     </row>
-    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="248" t="s">
-        <v>259</v>
+      <c r="B9" s="188" t="s">
+        <v>258</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
@@ -6148,10 +6148,10 @@
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
       <c r="J9" s="182" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>80</v>
       </c>
@@ -6166,10 +6166,10 @@
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
       <c r="J10" s="183" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -6181,36 +6181,36 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="218" t="s">
+    <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="220" t="s">
+      <c r="B12" s="241" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="222" t="s">
+      <c r="C12" s="243" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="224" t="s">
+      <c r="D12" s="232" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="225"/>
-      <c r="F12" s="226"/>
-      <c r="G12" s="224" t="s">
+      <c r="E12" s="233"/>
+      <c r="F12" s="234"/>
+      <c r="G12" s="232" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="225"/>
-      <c r="I12" s="226"/>
-      <c r="J12" s="231" t="s">
+      <c r="H12" s="233"/>
+      <c r="I12" s="234"/>
+      <c r="J12" s="235" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="200"/>
-      <c r="L12" s="200"/>
-    </row>
-    <row r="13" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="219"/>
-      <c r="B13" s="221"/>
-      <c r="C13" s="223"/>
+      <c r="K12" s="204"/>
+      <c r="L12" s="204"/>
+    </row>
+    <row r="13" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="240"/>
+      <c r="B13" s="242"/>
+      <c r="C13" s="244"/>
       <c r="D13" s="65" t="s">
         <v>11</v>
       </c>
@@ -6229,25 +6229,25 @@
       <c r="I13" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="232"/>
-      <c r="K13" s="200"/>
-      <c r="L13" s="200"/>
-    </row>
-    <row r="14" spans="1:12" s="66" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="227" t="s">
+      <c r="J13" s="236"/>
+      <c r="K13" s="204"/>
+      <c r="L13" s="204"/>
+    </row>
+    <row r="14" spans="1:12" s="66" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="228" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="227"/>
-      <c r="C14" s="227"/>
-      <c r="D14" s="227"/>
-      <c r="E14" s="227"/>
-      <c r="F14" s="227"/>
-      <c r="G14" s="227"/>
-      <c r="H14" s="227"/>
-      <c r="I14" s="227"/>
-      <c r="J14" s="227"/>
-    </row>
-    <row r="15" spans="1:12" s="71" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="228"/>
+      <c r="C14" s="228"/>
+      <c r="D14" s="228"/>
+      <c r="E14" s="228"/>
+      <c r="F14" s="228"/>
+      <c r="G14" s="228"/>
+      <c r="H14" s="228"/>
+      <c r="I14" s="228"/>
+      <c r="J14" s="228"/>
+    </row>
+    <row r="15" spans="1:12" s="71" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="67" t="s">
         <v>84</v>
       </c>
@@ -6261,7 +6261,7 @@
       <c r="I15" s="69"/>
       <c r="J15" s="69"/>
     </row>
-    <row r="16" spans="1:12" s="73" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" s="73" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="24" t="s">
         <v>85</v>
       </c>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="J16" s="28"/>
     </row>
-    <row r="17" spans="1:10" s="73" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="73" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
         <v>87</v>
       </c>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="J17" s="28"/>
     </row>
-    <row r="18" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="32" t="s">
         <v>88</v>
       </c>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="J18" s="28"/>
     </row>
-    <row r="19" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="32" t="s">
         <v>90</v>
       </c>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="J19" s="28"/>
     </row>
-    <row r="20" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="32" t="s">
         <v>91</v>
       </c>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="J20" s="28"/>
     </row>
-    <row r="21" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="24" t="s">
         <v>92</v>
       </c>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:10" s="29" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="29" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="74" t="s">
         <v>94</v>
       </c>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="J22" s="28"/>
     </row>
-    <row r="23" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="24" t="s">
         <v>96</v>
       </c>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="J23" s="28"/>
     </row>
-    <row r="24" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="24" t="s">
         <v>97</v>
       </c>
@@ -6473,7 +6473,7 @@
       <c r="I24" s="27"/>
       <c r="J24" s="28"/>
     </row>
-    <row r="25" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="75"/>
       <c r="B25" s="76"/>
       <c r="C25" s="77"/>
@@ -6485,21 +6485,21 @@
       <c r="I25" s="77"/>
       <c r="J25" s="78"/>
     </row>
-    <row r="26" spans="1:10" s="71" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="228" t="s">
+    <row r="26" spans="1:10" s="71" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="229" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="228"/>
-      <c r="C26" s="228"/>
-      <c r="D26" s="228"/>
-      <c r="E26" s="228"/>
-      <c r="F26" s="228"/>
-      <c r="G26" s="228"/>
-      <c r="H26" s="228"/>
-      <c r="I26" s="228"/>
-      <c r="J26" s="228"/>
-    </row>
-    <row r="27" spans="1:10" s="71" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="229"/>
+      <c r="C26" s="229"/>
+      <c r="D26" s="229"/>
+      <c r="E26" s="229"/>
+      <c r="F26" s="229"/>
+      <c r="G26" s="229"/>
+      <c r="H26" s="229"/>
+      <c r="I26" s="229"/>
+      <c r="J26" s="229"/>
+    </row>
+    <row r="27" spans="1:10" s="71" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="67" t="s">
         <v>101</v>
       </c>
@@ -6513,7 +6513,7 @@
       <c r="I27" s="69"/>
       <c r="J27" s="69"/>
     </row>
-    <row r="28" spans="1:10" s="58" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" s="58" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="79" t="s">
         <v>102</v>
       </c>
@@ -6527,7 +6527,7 @@
       <c r="I28" s="83"/>
       <c r="J28" s="84"/>
     </row>
-    <row r="29" spans="1:10" s="58" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="58" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="85" t="s">
         <v>103</v>
       </c>
@@ -6547,7 +6547,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="89"/>
     </row>
-    <row r="30" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="79" t="s">
         <v>106</v>
       </c>
@@ -6567,7 +6567,7 @@
       <c r="I30" s="83"/>
       <c r="J30" s="28"/>
     </row>
-    <row r="31" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="79" t="s">
         <v>108</v>
       </c>
@@ -6587,7 +6587,7 @@
       <c r="I31" s="83"/>
       <c r="J31" s="28"/>
     </row>
-    <row r="32" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="79" t="s">
         <v>110</v>
       </c>
@@ -6607,7 +6607,7 @@
       <c r="I32" s="83"/>
       <c r="J32" s="28"/>
     </row>
-    <row r="33" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="79" t="s">
         <v>112</v>
       </c>
@@ -6627,7 +6627,7 @@
       <c r="I33" s="94"/>
       <c r="J33" s="95"/>
     </row>
-    <row r="34" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="96" t="s">
         <v>114</v>
       </c>
@@ -6647,7 +6647,7 @@
       <c r="I34" s="34"/>
       <c r="J34" s="95"/>
     </row>
-    <row r="35" spans="1:10" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="23" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="67" t="s">
         <v>116</v>
       </c>
@@ -6661,7 +6661,7 @@
       <c r="I35" s="101"/>
       <c r="J35" s="67"/>
     </row>
-    <row r="36" spans="1:10" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" s="23" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="102" t="s">
         <v>117</v>
       </c>
@@ -6675,7 +6675,7 @@
       <c r="I36" s="101"/>
       <c r="J36" s="67"/>
     </row>
-    <row r="37" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="103" t="s">
         <v>118</v>
       </c>
@@ -6689,7 +6689,7 @@
       <c r="I37" s="83"/>
       <c r="J37" s="84"/>
     </row>
-    <row r="38" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="105" t="s">
         <v>119</v>
       </c>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="J38" s="89"/>
     </row>
-    <row r="39" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="106" t="s">
         <v>120</v>
       </c>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="J39" s="28"/>
     </row>
-    <row r="40" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="106" t="s">
         <v>121</v>
       </c>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="J40" s="28"/>
     </row>
-    <row r="41" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="105" t="s">
         <v>122</v>
       </c>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="J41" s="28"/>
     </row>
-    <row r="42" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="107" t="s">
         <v>123</v>
       </c>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="J42" s="84"/>
     </row>
-    <row r="43" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="107" t="s">
         <v>125</v>
       </c>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="J43" s="84"/>
     </row>
-    <row r="44" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="79" t="s">
         <v>127</v>
       </c>
@@ -6827,7 +6827,7 @@
       <c r="I44" s="109"/>
       <c r="J44" s="84"/>
     </row>
-    <row r="45" spans="1:10" s="115" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" s="115" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="85" t="s">
         <v>128</v>
       </c>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="J45" s="114"/>
     </row>
-    <row r="46" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="116" t="s">
         <v>130</v>
       </c>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="J46" s="89"/>
     </row>
-    <row r="47" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="118" t="s">
         <v>132</v>
       </c>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="J47" s="84"/>
     </row>
-    <row r="48" spans="1:10" s="60" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" s="60" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="119" t="s">
         <v>134</v>
       </c>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="J48" s="28"/>
     </row>
-    <row r="49" spans="1:10" s="58" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" s="58" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="96" t="s">
         <v>136</v>
       </c>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="J49" s="28"/>
     </row>
-    <row r="50" spans="1:10" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" s="23" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="102" t="s">
         <v>138</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="51" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="121" t="s">
         <v>140</v>
       </c>
@@ -6977,7 +6977,7 @@
       <c r="I51" s="125"/>
       <c r="J51" s="126"/>
     </row>
-    <row r="52" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="116" t="s">
         <v>141</v>
       </c>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="J52" s="89"/>
     </row>
-    <row r="53" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="121" t="s">
         <v>143</v>
       </c>
@@ -7013,7 +7013,7 @@
       <c r="I53" s="127"/>
       <c r="J53" s="126"/>
     </row>
-    <row r="54" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="116" t="s">
         <v>144</v>
       </c>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="J54" s="89"/>
     </row>
-    <row r="55" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="116" t="s">
         <v>146</v>
       </c>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="J55" s="89"/>
     </row>
-    <row r="56" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="128" t="s">
         <v>148</v>
       </c>
@@ -7071,7 +7071,7 @@
       <c r="I56" s="127"/>
       <c r="J56" s="132"/>
     </row>
-    <row r="57" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="116" t="s">
         <v>149</v>
       </c>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="J57" s="89"/>
     </row>
-    <row r="58" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="133" t="s">
         <v>151</v>
       </c>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="J58" s="137"/>
     </row>
-    <row r="59" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="119" t="s">
         <v>153</v>
       </c>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="J59" s="28"/>
     </row>
-    <row r="60" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="128" t="s">
         <v>155</v>
       </c>
@@ -7151,7 +7151,7 @@
       <c r="I60" s="127"/>
       <c r="J60" s="132"/>
     </row>
-    <row r="61" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="116" t="s">
         <v>156</v>
       </c>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="J61" s="89"/>
     </row>
-    <row r="62" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="118" t="s">
         <v>158</v>
       </c>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="J62" s="28"/>
     </row>
-    <row r="63" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="118" t="s">
         <v>160</v>
       </c>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="J63" s="28"/>
     </row>
-    <row r="64" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="121" t="s">
         <v>162</v>
       </c>
@@ -7231,7 +7231,7 @@
       <c r="I64" s="127"/>
       <c r="J64" s="126"/>
     </row>
-    <row r="65" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="116" t="s">
         <v>163</v>
       </c>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="J65" s="89"/>
     </row>
-    <row r="66" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="118" t="s">
         <v>165</v>
       </c>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="J66" s="28"/>
     </row>
-    <row r="67" spans="1:10" s="73" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" s="73" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="121" t="s">
         <v>167</v>
       </c>
@@ -7289,7 +7289,7 @@
       <c r="I67" s="138"/>
       <c r="J67" s="144"/>
     </row>
-    <row r="68" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="116" t="s">
         <v>168</v>
       </c>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="J68" s="89"/>
     </row>
-    <row r="69" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="118" t="s">
         <v>170</v>
       </c>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="J69" s="28"/>
     </row>
-    <row r="70" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="121" t="s">
         <v>172</v>
       </c>
@@ -7347,7 +7347,7 @@
       <c r="I70" s="127"/>
       <c r="J70" s="126"/>
     </row>
-    <row r="71" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="145" t="s">
         <v>173</v>
       </c>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="J71" s="89"/>
     </row>
-    <row r="72" spans="1:10" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" s="23" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="102" t="s">
         <v>175</v>
       </c>
@@ -7383,7 +7383,7 @@
       <c r="I72" s="101"/>
       <c r="J72" s="67"/>
     </row>
-    <row r="73" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="121" t="s">
         <v>176</v>
       </c>
@@ -7397,7 +7397,7 @@
       <c r="I73" s="127"/>
       <c r="J73" s="126"/>
     </row>
-    <row r="74" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="116" t="s">
         <v>177</v>
       </c>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="J74" s="89"/>
     </row>
-    <row r="75" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="118" t="s">
         <v>179</v>
       </c>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="J75" s="28"/>
     </row>
-    <row r="76" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="118" t="s">
         <v>181</v>
       </c>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="J76" s="28"/>
     </row>
-    <row r="77" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="121" t="s">
         <v>183</v>
       </c>
@@ -7477,7 +7477,7 @@
       <c r="I77" s="125"/>
       <c r="J77" s="126"/>
     </row>
-    <row r="78" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="116" t="s">
         <v>184</v>
       </c>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="J78" s="89"/>
     </row>
-    <row r="79" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="119" t="s">
         <v>186</v>
       </c>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="J79" s="28"/>
     </row>
-    <row r="80" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="119" t="s">
         <v>188</v>
       </c>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="J80" s="28"/>
     </row>
-    <row r="81" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="119" t="s">
         <v>190</v>
       </c>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="J81" s="28"/>
     </row>
-    <row r="82" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="121" t="s">
         <v>192</v>
       </c>
@@ -7579,7 +7579,7 @@
       <c r="I82" s="125"/>
       <c r="J82" s="126"/>
     </row>
-    <row r="83" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="133" t="s">
         <v>193</v>
       </c>
@@ -7595,7 +7595,7 @@
       <c r="I83" s="109"/>
       <c r="J83" s="137"/>
     </row>
-    <row r="84" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="116" t="s">
         <v>195</v>
       </c>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="J84" s="89"/>
     </row>
-    <row r="85" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="147" t="s">
         <v>197</v>
       </c>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="J85" s="28"/>
     </row>
-    <row r="86" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="147" t="s">
         <v>199</v>
       </c>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="J86" s="28"/>
     </row>
-    <row r="87" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="147" t="s">
         <v>200</v>
       </c>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="J87" s="28"/>
     </row>
-    <row r="88" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" s="60" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="147" t="s">
         <v>202</v>
       </c>
@@ -7705,11 +7705,11 @@
       </c>
       <c r="J88" s="28"/>
     </row>
-    <row r="89" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="229" t="s">
+    <row r="89" spans="1:10" s="29" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="230" t="s">
         <v>204</v>
       </c>
-      <c r="B89" s="230"/>
+      <c r="B89" s="231"/>
       <c r="C89" s="149"/>
       <c r="D89" s="150"/>
       <c r="E89" s="150"/>
@@ -7719,15 +7719,15 @@
       <c r="I89" s="127"/>
       <c r="J89" s="126"/>
     </row>
-    <row r="90" spans="1:10" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="216" t="s">
+    <row r="90" spans="1:10" s="60" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="237" t="s">
         <v>205</v>
       </c>
-      <c r="B90" s="216"/>
-      <c r="C90" s="216"/>
-      <c r="D90" s="216"/>
-      <c r="E90" s="216"/>
-      <c r="F90" s="217"/>
+      <c r="B90" s="237"/>
+      <c r="C90" s="237"/>
+      <c r="D90" s="237"/>
+      <c r="E90" s="237"/>
+      <c r="F90" s="238"/>
       <c r="G90" s="30" t="s">
         <v>19</v>
       </c>
@@ -7741,7 +7741,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="91" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" s="60" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="151"/>
       <c r="B91" s="151"/>
       <c r="C91" s="151"/>
@@ -7752,7 +7752,7 @@
       <c r="H91" s="59"/>
       <c r="I91" s="59"/>
     </row>
-    <row r="92" spans="1:10" s="71" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" s="71" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="152" t="s">
         <v>207</v>
       </c>
@@ -7766,7 +7766,7 @@
       <c r="I92" s="152"/>
       <c r="J92" s="152"/>
     </row>
-    <row r="93" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="153" t="s">
         <v>208</v>
       </c>
@@ -7780,7 +7780,7 @@
       <c r="I93" s="78"/>
       <c r="J93" s="78"/>
     </row>
-    <row r="94" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="153" t="s">
         <v>209</v>
       </c>
@@ -7794,7 +7794,7 @@
       <c r="I94" s="78"/>
       <c r="J94" s="78"/>
     </row>
-    <row r="95" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="153"/>
       <c r="B95" s="76"/>
       <c r="C95" s="78"/>
@@ -7806,7 +7806,7 @@
       <c r="I95" s="78"/>
       <c r="J95" s="78"/>
     </row>
-    <row r="96" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="154" t="s">
         <v>210</v>
       </c>
@@ -7820,7 +7820,7 @@
       <c r="I96" s="156"/>
       <c r="J96" s="156"/>
     </row>
-    <row r="97" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="67" t="s">
         <v>211</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="98" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="153" t="s">
         <v>216</v>
       </c>
@@ -7864,7 +7864,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="99" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="153" t="s">
         <v>220</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="100" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="153" t="s">
         <v>221</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="153" t="s">
         <v>223</v>
       </c>
@@ -7924,7 +7924,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="102" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="153" t="s">
         <v>224</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="103" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="153" t="s">
         <v>225</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="104" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="159"/>
       <c r="B104" s="160"/>
       <c r="C104" s="161"/>
@@ -7976,7 +7976,7 @@
       <c r="I104" s="161"/>
       <c r="J104" s="161"/>
     </row>
-    <row r="105" spans="1:10" s="165" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" s="165" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="162" t="s">
         <v>227</v>
       </c>
@@ -7992,8 +7992,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="119" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B119" s="60"/>
       <c r="C119" s="60"/>
       <c r="D119" s="60"/>
@@ -8004,7 +8004,7 @@
       <c r="I119" s="60"/>
       <c r="J119" s="60"/>
     </row>
-    <row r="120" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="60"/>
       <c r="C120" s="60"/>
       <c r="D120" s="60"/>
@@ -8015,7 +8015,7 @@
       <c r="I120" s="60"/>
       <c r="J120" s="60"/>
     </row>
-    <row r="121" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B121" s="60"/>
       <c r="C121" s="60"/>
       <c r="D121" s="60"/>
@@ -8026,7 +8026,7 @@
       <c r="I121" s="60"/>
       <c r="J121" s="60"/>
     </row>
-    <row r="122" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B122" s="60"/>
       <c r="C122" s="60"/>
       <c r="D122" s="60"/>
@@ -8037,7 +8037,7 @@
       <c r="I122" s="60"/>
       <c r="J122" s="60"/>
     </row>
-    <row r="123" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B123" s="60"/>
       <c r="C123" s="60"/>
       <c r="D123" s="60"/>
@@ -8048,7 +8048,7 @@
       <c r="I123" s="60"/>
       <c r="J123" s="60"/>
     </row>
-    <row r="124" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B124" s="60"/>
       <c r="C124" s="60"/>
       <c r="D124" s="60"/>
@@ -8059,7 +8059,7 @@
       <c r="I124" s="60"/>
       <c r="J124" s="60"/>
     </row>
-    <row r="125" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B125" s="60"/>
       <c r="C125" s="60"/>
       <c r="D125" s="60"/>
@@ -8070,7 +8070,7 @@
       <c r="I125" s="60"/>
       <c r="J125" s="60"/>
     </row>
-    <row r="126" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="60"/>
       <c r="C126" s="60"/>
       <c r="D126" s="60"/>
@@ -8081,7 +8081,7 @@
       <c r="I126" s="60"/>
       <c r="J126" s="60"/>
     </row>
-    <row r="127" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B127" s="60"/>
       <c r="C127" s="60"/>
       <c r="D127" s="60"/>
@@ -8092,7 +8092,7 @@
       <c r="I127" s="60"/>
       <c r="J127" s="60"/>
     </row>
-    <row r="128" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B128" s="60"/>
       <c r="C128" s="60"/>
       <c r="D128" s="60"/>
@@ -8103,7 +8103,7 @@
       <c r="I128" s="60"/>
       <c r="J128" s="60"/>
     </row>
-    <row r="129" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B129" s="60"/>
       <c r="C129" s="60"/>
       <c r="D129" s="60"/>
@@ -8114,7 +8114,7 @@
       <c r="I129" s="60"/>
       <c r="J129" s="60"/>
     </row>
-    <row r="130" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B130" s="60"/>
       <c r="C130" s="60"/>
       <c r="D130" s="60"/>
@@ -8125,7 +8125,7 @@
       <c r="I130" s="60"/>
       <c r="J130" s="60"/>
     </row>
-    <row r="131" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B131" s="60"/>
       <c r="C131" s="60"/>
       <c r="D131" s="60"/>
@@ -8136,7 +8136,7 @@
       <c r="I131" s="60"/>
       <c r="J131" s="60"/>
     </row>
-    <row r="132" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B132" s="60"/>
       <c r="C132" s="60"/>
       <c r="D132" s="60"/>
@@ -8147,7 +8147,7 @@
       <c r="I132" s="60"/>
       <c r="J132" s="60"/>
     </row>
-    <row r="133" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B133" s="60"/>
       <c r="C133" s="60"/>
       <c r="D133" s="60"/>
@@ -8158,7 +8158,7 @@
       <c r="I133" s="60"/>
       <c r="J133" s="60"/>
     </row>
-    <row r="134" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B134" s="60"/>
       <c r="C134" s="60"/>
       <c r="D134" s="60"/>
@@ -8169,7 +8169,7 @@
       <c r="I134" s="60"/>
       <c r="J134" s="60"/>
     </row>
-    <row r="135" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B135" s="60"/>
       <c r="C135" s="60"/>
       <c r="D135" s="60"/>
@@ -8180,7 +8180,7 @@
       <c r="I135" s="60"/>
       <c r="J135" s="60"/>
     </row>
-    <row r="136" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B136" s="60"/>
       <c r="C136" s="60"/>
       <c r="D136" s="60"/>
@@ -8191,7 +8191,7 @@
       <c r="I136" s="60"/>
       <c r="J136" s="60"/>
     </row>
-    <row r="137" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B137" s="60"/>
       <c r="C137" s="60"/>
       <c r="D137" s="60"/>
@@ -8202,7 +8202,7 @@
       <c r="I137" s="60"/>
       <c r="J137" s="60"/>
     </row>
-    <row r="138" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B138" s="60"/>
       <c r="C138" s="60"/>
       <c r="D138" s="60"/>
@@ -8213,7 +8213,7 @@
       <c r="I138" s="60"/>
       <c r="J138" s="60"/>
     </row>
-    <row r="139" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B139" s="60"/>
       <c r="C139" s="60"/>
       <c r="D139" s="60"/>
@@ -8224,7 +8224,7 @@
       <c r="I139" s="60"/>
       <c r="J139" s="60"/>
     </row>
-    <row r="140" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B140" s="60"/>
       <c r="C140" s="60"/>
       <c r="D140" s="60"/>
@@ -8235,7 +8235,7 @@
       <c r="I140" s="60"/>
       <c r="J140" s="60"/>
     </row>
-    <row r="141" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B141" s="60"/>
       <c r="C141" s="60"/>
       <c r="D141" s="60"/>
@@ -8246,7 +8246,7 @@
       <c r="I141" s="60"/>
       <c r="J141" s="60"/>
     </row>
-    <row r="142" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B142" s="60"/>
       <c r="C142" s="60"/>
       <c r="D142" s="60"/>
@@ -8257,7 +8257,7 @@
       <c r="I142" s="60"/>
       <c r="J142" s="60"/>
     </row>
-    <row r="143" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B143" s="60"/>
       <c r="C143" s="60"/>
       <c r="D143" s="60"/>
@@ -8268,7 +8268,7 @@
       <c r="I143" s="60"/>
       <c r="J143" s="60"/>
     </row>
-    <row r="144" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B144" s="60"/>
       <c r="C144" s="60"/>
       <c r="D144" s="60"/>
@@ -8279,7 +8279,7 @@
       <c r="I144" s="60"/>
       <c r="J144" s="60"/>
     </row>
-    <row r="145" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B145" s="60"/>
       <c r="C145" s="60"/>
       <c r="D145" s="60"/>
@@ -8290,7 +8290,7 @@
       <c r="I145" s="60"/>
       <c r="J145" s="60"/>
     </row>
-    <row r="146" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="60"/>
       <c r="C146" s="60"/>
       <c r="D146" s="60"/>
@@ -8301,7 +8301,7 @@
       <c r="I146" s="60"/>
       <c r="J146" s="60"/>
     </row>
-    <row r="147" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="60"/>
       <c r="C147" s="60"/>
       <c r="D147" s="60"/>
@@ -8312,7 +8312,7 @@
       <c r="I147" s="60"/>
       <c r="J147" s="60"/>
     </row>
-    <row r="148" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B148" s="60"/>
       <c r="C148" s="60"/>
       <c r="D148" s="60"/>
@@ -8323,7 +8323,7 @@
       <c r="I148" s="60"/>
       <c r="J148" s="60"/>
     </row>
-    <row r="149" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B149" s="60"/>
       <c r="C149" s="60"/>
       <c r="D149" s="60"/>
@@ -8334,7 +8334,7 @@
       <c r="I149" s="60"/>
       <c r="J149" s="60"/>
     </row>
-    <row r="150" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B150" s="60"/>
       <c r="C150" s="60"/>
       <c r="D150" s="60"/>
@@ -8345,7 +8345,7 @@
       <c r="I150" s="60"/>
       <c r="J150" s="60"/>
     </row>
-    <row r="151" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B151" s="60"/>
       <c r="C151" s="60"/>
       <c r="D151" s="60"/>
@@ -8356,7 +8356,7 @@
       <c r="I151" s="60"/>
       <c r="J151" s="60"/>
     </row>
-    <row r="152" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B152" s="60"/>
       <c r="C152" s="60"/>
       <c r="D152" s="60"/>
@@ -8367,7 +8367,7 @@
       <c r="I152" s="60"/>
       <c r="J152" s="60"/>
     </row>
-    <row r="153" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B153" s="60"/>
       <c r="C153" s="60"/>
       <c r="D153" s="60"/>
@@ -8378,7 +8378,7 @@
       <c r="I153" s="60"/>
       <c r="J153" s="60"/>
     </row>
-    <row r="154" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B154" s="60"/>
       <c r="C154" s="60"/>
       <c r="D154" s="60"/>
@@ -8389,7 +8389,7 @@
       <c r="I154" s="60"/>
       <c r="J154" s="60"/>
     </row>
-    <row r="155" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B155" s="60"/>
       <c r="C155" s="60"/>
       <c r="D155" s="60"/>
@@ -8400,7 +8400,7 @@
       <c r="I155" s="60"/>
       <c r="J155" s="60"/>
     </row>
-    <row r="156" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B156" s="60"/>
       <c r="C156" s="60"/>
       <c r="D156" s="60"/>
@@ -8411,7 +8411,7 @@
       <c r="I156" s="60"/>
       <c r="J156" s="60"/>
     </row>
-    <row r="157" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B157" s="60"/>
       <c r="C157" s="60"/>
       <c r="D157" s="60"/>
@@ -8422,7 +8422,7 @@
       <c r="I157" s="60"/>
       <c r="J157" s="60"/>
     </row>
-    <row r="158" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B158" s="60"/>
       <c r="C158" s="60"/>
       <c r="D158" s="60"/>
@@ -8433,7 +8433,7 @@
       <c r="I158" s="60"/>
       <c r="J158" s="60"/>
     </row>
-    <row r="159" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B159" s="60"/>
       <c r="C159" s="60"/>
       <c r="D159" s="60"/>
@@ -8444,7 +8444,7 @@
       <c r="I159" s="60"/>
       <c r="J159" s="60"/>
     </row>
-    <row r="160" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B160" s="60"/>
       <c r="C160" s="60"/>
       <c r="D160" s="60"/>
@@ -8455,7 +8455,7 @@
       <c r="I160" s="60"/>
       <c r="J160" s="60"/>
     </row>
-    <row r="161" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="60"/>
       <c r="C161" s="60"/>
       <c r="D161" s="60"/>
@@ -8466,7 +8466,7 @@
       <c r="I161" s="60"/>
       <c r="J161" s="60"/>
     </row>
-    <row r="162" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B162" s="60"/>
       <c r="C162" s="60"/>
       <c r="D162" s="60"/>
@@ -8477,7 +8477,7 @@
       <c r="I162" s="60"/>
       <c r="J162" s="60"/>
     </row>
-    <row r="163" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B163" s="60"/>
       <c r="C163" s="60"/>
       <c r="D163" s="60"/>
@@ -8488,7 +8488,7 @@
       <c r="I163" s="60"/>
       <c r="J163" s="60"/>
     </row>
-    <row r="164" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B164" s="60"/>
       <c r="C164" s="60"/>
       <c r="D164" s="60"/>
@@ -8499,7 +8499,7 @@
       <c r="I164" s="60"/>
       <c r="J164" s="60"/>
     </row>
-    <row r="165" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B165" s="60"/>
       <c r="C165" s="60"/>
       <c r="D165" s="60"/>
@@ -8510,7 +8510,7 @@
       <c r="I165" s="60"/>
       <c r="J165" s="60"/>
     </row>
-    <row r="166" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B166" s="60"/>
       <c r="C166" s="60"/>
       <c r="D166" s="60"/>
@@ -8521,7 +8521,7 @@
       <c r="I166" s="60"/>
       <c r="J166" s="60"/>
     </row>
-    <row r="167" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B167" s="60"/>
       <c r="C167" s="60"/>
       <c r="D167" s="60"/>
@@ -8532,7 +8532,7 @@
       <c r="I167" s="60"/>
       <c r="J167" s="60"/>
     </row>
-    <row r="168" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B168" s="60"/>
       <c r="C168" s="60"/>
       <c r="D168" s="60"/>
@@ -8543,7 +8543,7 @@
       <c r="I168" s="60"/>
       <c r="J168" s="60"/>
     </row>
-    <row r="169" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B169" s="60"/>
       <c r="C169" s="60"/>
       <c r="D169" s="60"/>
@@ -8554,7 +8554,7 @@
       <c r="I169" s="60"/>
       <c r="J169" s="60"/>
     </row>
-    <row r="170" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B170" s="60"/>
       <c r="C170" s="60"/>
       <c r="D170" s="60"/>
@@ -8565,7 +8565,7 @@
       <c r="I170" s="60"/>
       <c r="J170" s="60"/>
     </row>
-    <row r="171" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B171" s="60"/>
       <c r="C171" s="60"/>
       <c r="D171" s="60"/>
@@ -8576,7 +8576,7 @@
       <c r="I171" s="60"/>
       <c r="J171" s="60"/>
     </row>
-    <row r="172" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B172" s="60"/>
       <c r="C172" s="60"/>
       <c r="D172" s="60"/>
@@ -8587,7 +8587,7 @@
       <c r="I172" s="60"/>
       <c r="J172" s="60"/>
     </row>
-    <row r="173" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B173" s="60"/>
       <c r="C173" s="60"/>
       <c r="D173" s="60"/>
@@ -8598,7 +8598,7 @@
       <c r="I173" s="60"/>
       <c r="J173" s="60"/>
     </row>
-    <row r="174" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B174" s="60"/>
       <c r="C174" s="60"/>
       <c r="D174" s="60"/>
@@ -8609,7 +8609,7 @@
       <c r="I174" s="60"/>
       <c r="J174" s="60"/>
     </row>
-    <row r="175" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B175" s="60"/>
       <c r="C175" s="60"/>
       <c r="D175" s="60"/>
@@ -8620,7 +8620,7 @@
       <c r="I175" s="60"/>
       <c r="J175" s="60"/>
     </row>
-    <row r="176" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B176" s="60"/>
       <c r="C176" s="60"/>
       <c r="D176" s="60"/>
@@ -8631,7 +8631,7 @@
       <c r="I176" s="60"/>
       <c r="J176" s="60"/>
     </row>
-    <row r="177" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B177" s="60"/>
       <c r="C177" s="60"/>
       <c r="D177" s="60"/>
@@ -8642,7 +8642,7 @@
       <c r="I177" s="60"/>
       <c r="J177" s="60"/>
     </row>
-    <row r="178" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B178" s="60"/>
       <c r="C178" s="60"/>
       <c r="D178" s="60"/>
@@ -8653,651 +8653,656 @@
       <c r="I178" s="60"/>
       <c r="J178" s="60"/>
     </row>
-    <row r="179" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B179" s="60"/>
       <c r="G179" s="42"/>
     </row>
-    <row r="180" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B180" s="60"/>
       <c r="G180" s="42"/>
     </row>
-    <row r="181" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B181" s="60"/>
       <c r="G181" s="42"/>
     </row>
-    <row r="182" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B182" s="60"/>
       <c r="G182" s="42"/>
     </row>
-    <row r="183" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B183" s="60"/>
       <c r="G183" s="42"/>
     </row>
-    <row r="184" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B184" s="60"/>
       <c r="G184" s="42"/>
     </row>
-    <row r="185" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B185" s="60"/>
       <c r="G185" s="42"/>
     </row>
-    <row r="186" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B186" s="60"/>
       <c r="G186" s="42"/>
     </row>
-    <row r="187" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B187" s="60"/>
       <c r="G187" s="42"/>
     </row>
-    <row r="188" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B188" s="60"/>
       <c r="G188" s="42"/>
     </row>
-    <row r="189" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B189" s="60"/>
       <c r="G189" s="42"/>
     </row>
-    <row r="190" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B190" s="60"/>
       <c r="G190" s="42"/>
     </row>
-    <row r="191" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B191" s="60"/>
       <c r="G191" s="42"/>
     </row>
-    <row r="192" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B192" s="60"/>
       <c r="G192" s="42"/>
     </row>
-    <row r="193" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B193" s="60"/>
       <c r="G193" s="42"/>
     </row>
-    <row r="194" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B194" s="60"/>
       <c r="G194" s="42"/>
     </row>
-    <row r="195" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B195" s="60"/>
       <c r="G195" s="42"/>
     </row>
-    <row r="196" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B196" s="60"/>
       <c r="G196" s="42"/>
     </row>
-    <row r="197" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B197" s="60"/>
       <c r="G197" s="42"/>
     </row>
-    <row r="198" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B198" s="60"/>
       <c r="G198" s="42"/>
     </row>
-    <row r="199" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B199" s="60"/>
       <c r="G199" s="42"/>
     </row>
-    <row r="200" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B200" s="60"/>
       <c r="G200" s="42"/>
     </row>
-    <row r="201" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B201" s="60"/>
       <c r="G201" s="42"/>
     </row>
-    <row r="202" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B202" s="60"/>
       <c r="G202" s="42"/>
     </row>
-    <row r="203" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B203" s="60"/>
       <c r="G203" s="42"/>
     </row>
-    <row r="204" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B204" s="60"/>
       <c r="G204" s="42"/>
     </row>
-    <row r="205" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B205" s="60"/>
       <c r="G205" s="42"/>
     </row>
-    <row r="206" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B206" s="60"/>
       <c r="G206" s="42"/>
     </row>
-    <row r="207" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B207" s="60"/>
       <c r="G207" s="42"/>
     </row>
-    <row r="208" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B208" s="60"/>
       <c r="G208" s="42"/>
     </row>
-    <row r="209" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B209" s="60"/>
       <c r="G209" s="42"/>
     </row>
-    <row r="210" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B210" s="60"/>
       <c r="G210" s="42"/>
     </row>
-    <row r="211" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B211" s="60"/>
       <c r="G211" s="42"/>
     </row>
-    <row r="212" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B212" s="60"/>
       <c r="G212" s="42"/>
     </row>
-    <row r="213" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B213" s="60"/>
       <c r="G213" s="42"/>
     </row>
-    <row r="214" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B214" s="60"/>
       <c r="G214" s="42"/>
     </row>
-    <row r="215" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B215" s="60"/>
       <c r="G215" s="42"/>
     </row>
-    <row r="216" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B216" s="60"/>
       <c r="G216" s="42"/>
     </row>
-    <row r="217" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B217" s="60"/>
       <c r="G217" s="42"/>
     </row>
-    <row r="218" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B218" s="60"/>
       <c r="G218" s="42"/>
     </row>
-    <row r="219" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B219" s="60"/>
       <c r="G219" s="42"/>
     </row>
-    <row r="220" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B220" s="60"/>
       <c r="G220" s="42"/>
     </row>
-    <row r="221" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B221" s="60"/>
       <c r="G221" s="42"/>
     </row>
-    <row r="222" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B222" s="60"/>
       <c r="G222" s="42"/>
     </row>
-    <row r="223" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B223" s="60"/>
       <c r="G223" s="42"/>
     </row>
-    <row r="224" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B224" s="60"/>
       <c r="G224" s="42"/>
     </row>
-    <row r="225" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B225" s="60"/>
       <c r="G225" s="42"/>
     </row>
-    <row r="226" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B226" s="60"/>
       <c r="G226" s="42"/>
     </row>
-    <row r="227" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B227" s="60"/>
       <c r="G227" s="42"/>
     </row>
-    <row r="228" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G228" s="42"/>
     </row>
-    <row r="229" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G229" s="42"/>
     </row>
-    <row r="230" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G230" s="42"/>
     </row>
-    <row r="231" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G231" s="42"/>
     </row>
-    <row r="232" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G232" s="42"/>
     </row>
-    <row r="233" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G233" s="42"/>
     </row>
-    <row r="234" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G234" s="42"/>
     </row>
-    <row r="235" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G235" s="42"/>
     </row>
-    <row r="236" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G236" s="42"/>
     </row>
-    <row r="237" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G237" s="42"/>
     </row>
-    <row r="238" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G238" s="42"/>
     </row>
-    <row r="239" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G239" s="42"/>
     </row>
-    <row r="240" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G240" s="42"/>
     </row>
-    <row r="241" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G241" s="42"/>
     </row>
-    <row r="242" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G242" s="42"/>
     </row>
-    <row r="243" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G243" s="42"/>
     </row>
-    <row r="244" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G244" s="42"/>
     </row>
-    <row r="245" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G245" s="42"/>
     </row>
-    <row r="246" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G246" s="42"/>
     </row>
-    <row r="247" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G247" s="42"/>
     </row>
-    <row r="248" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G248" s="42"/>
     </row>
-    <row r="249" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G249" s="42"/>
     </row>
-    <row r="250" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G250" s="42"/>
     </row>
-    <row r="251" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G251" s="42"/>
     </row>
-    <row r="252" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G252" s="42"/>
     </row>
-    <row r="253" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G253" s="42"/>
     </row>
-    <row r="254" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G254" s="42"/>
     </row>
-    <row r="255" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G255" s="42"/>
     </row>
-    <row r="256" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G256" s="42"/>
     </row>
-    <row r="257" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G257" s="42"/>
     </row>
-    <row r="258" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G258" s="42"/>
     </row>
-    <row r="259" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G259" s="42"/>
     </row>
-    <row r="260" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G260" s="42"/>
     </row>
-    <row r="261" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G261" s="42"/>
     </row>
-    <row r="262" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G262" s="42"/>
     </row>
-    <row r="263" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G263" s="42"/>
     </row>
-    <row r="264" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G264" s="42"/>
     </row>
-    <row r="265" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G265" s="42"/>
     </row>
-    <row r="266" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G266" s="42"/>
     </row>
-    <row r="267" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G267" s="42"/>
     </row>
-    <row r="268" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G268" s="42"/>
     </row>
-    <row r="269" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G269" s="42"/>
     </row>
-    <row r="270" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G270" s="42"/>
     </row>
-    <row r="271" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G271" s="42"/>
     </row>
-    <row r="272" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G272" s="42"/>
     </row>
-    <row r="273" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G273" s="42"/>
     </row>
-    <row r="274" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G274" s="42"/>
     </row>
-    <row r="275" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G275" s="42"/>
     </row>
-    <row r="276" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G276" s="42"/>
     </row>
-    <row r="277" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G277" s="42"/>
     </row>
-    <row r="278" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G278" s="42"/>
     </row>
-    <row r="279" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G279" s="42"/>
     </row>
-    <row r="280" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G280" s="42"/>
     </row>
-    <row r="281" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G281" s="42"/>
     </row>
-    <row r="282" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G282" s="42"/>
     </row>
-    <row r="283" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G283" s="42"/>
     </row>
-    <row r="284" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G284" s="42"/>
     </row>
-    <row r="285" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G285" s="42"/>
     </row>
-    <row r="286" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G286" s="42"/>
     </row>
-    <row r="287" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G287" s="42"/>
     </row>
-    <row r="288" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G288" s="42"/>
     </row>
-    <row r="289" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G289" s="42"/>
     </row>
-    <row r="290" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G290" s="42"/>
     </row>
-    <row r="291" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G291" s="42"/>
     </row>
-    <row r="292" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G292" s="42"/>
     </row>
-    <row r="293" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G293" s="42"/>
     </row>
-    <row r="294" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G294" s="42"/>
     </row>
-    <row r="295" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G295" s="42"/>
     </row>
-    <row r="296" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G296" s="42"/>
     </row>
-    <row r="297" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G297" s="42"/>
     </row>
-    <row r="298" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G298" s="42"/>
     </row>
-    <row r="299" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G299" s="42"/>
     </row>
-    <row r="300" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G300" s="42"/>
     </row>
-    <row r="301" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G301" s="42"/>
     </row>
-    <row r="302" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G302" s="42"/>
     </row>
-    <row r="303" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G303" s="42"/>
     </row>
-    <row r="304" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G304" s="42"/>
     </row>
-    <row r="305" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G305" s="42"/>
     </row>
-    <row r="306" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G306" s="42"/>
     </row>
-    <row r="307" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G307" s="42"/>
     </row>
-    <row r="308" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G308" s="42"/>
     </row>
-    <row r="309" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G309" s="42"/>
     </row>
-    <row r="310" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G310" s="42"/>
     </row>
-    <row r="311" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G311" s="42"/>
     </row>
-    <row r="312" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G312" s="42"/>
     </row>
-    <row r="313" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G313" s="42"/>
     </row>
-    <row r="314" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G314" s="42"/>
     </row>
-    <row r="315" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G315" s="42"/>
     </row>
-    <row r="316" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G316" s="42"/>
     </row>
-    <row r="317" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G317" s="42"/>
     </row>
-    <row r="318" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G318" s="42"/>
     </row>
-    <row r="319" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G319" s="42"/>
     </row>
-    <row r="320" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G320" s="42"/>
     </row>
-    <row r="321" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G321" s="42"/>
     </row>
-    <row r="322" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G322" s="42"/>
     </row>
-    <row r="323" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G323" s="42"/>
     </row>
-    <row r="324" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G324" s="42"/>
     </row>
-    <row r="325" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G325" s="42"/>
     </row>
-    <row r="326" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G326" s="42"/>
     </row>
-    <row r="327" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G327" s="42"/>
     </row>
-    <row r="328" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G328" s="42"/>
     </row>
-    <row r="329" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G329" s="42"/>
     </row>
-    <row r="330" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G330" s="42"/>
     </row>
-    <row r="331" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G331" s="42"/>
     </row>
-    <row r="332" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G332" s="42"/>
     </row>
-    <row r="333" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G333" s="42"/>
     </row>
-    <row r="334" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G334" s="42"/>
     </row>
-    <row r="335" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G335" s="42"/>
     </row>
-    <row r="336" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G336" s="42"/>
     </row>
-    <row r="337" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G337" s="42"/>
     </row>
-    <row r="338" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G338" s="42"/>
     </row>
-    <row r="339" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G339" s="42"/>
     </row>
-    <row r="340" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G340" s="42"/>
     </row>
-    <row r="341" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G341" s="42"/>
     </row>
-    <row r="342" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G342" s="42"/>
     </row>
-    <row r="343" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G343" s="42"/>
     </row>
-    <row r="344" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G344" s="42"/>
     </row>
-    <row r="345" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G345" s="42"/>
     </row>
-    <row r="346" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G346" s="42"/>
     </row>
-    <row r="347" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G347" s="42"/>
     </row>
-    <row r="348" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G348" s="42"/>
     </row>
-    <row r="349" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G349" s="42"/>
     </row>
-    <row r="350" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G350" s="42"/>
     </row>
-    <row r="351" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G351" s="42"/>
     </row>
-    <row r="352" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G352" s="42"/>
     </row>
-    <row r="353" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G353" s="42"/>
     </row>
-    <row r="354" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G354" s="42"/>
     </row>
-    <row r="355" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G355" s="42"/>
     </row>
-    <row r="356" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G356" s="42"/>
     </row>
-    <row r="357" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G357" s="42"/>
     </row>
-    <row r="358" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G358" s="42"/>
     </row>
-    <row r="359" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G359" s="42"/>
     </row>
-    <row r="360" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G360" s="42"/>
     </row>
-    <row r="361" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G361" s="42"/>
     </row>
-    <row r="362" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G362" s="42"/>
     </row>
-    <row r="363" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G363" s="42"/>
     </row>
-    <row r="364" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G364" s="42"/>
     </row>
-    <row r="365" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G365" s="42"/>
     </row>
-    <row r="366" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G366" s="42"/>
     </row>
-    <row r="367" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G367" s="42"/>
     </row>
-    <row r="368" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G368" s="42"/>
     </row>
-    <row r="369" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G369" s="42"/>
     </row>
-    <row r="370" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G370" s="42"/>
     </row>
-    <row r="371" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G371" s="42"/>
     </row>
-    <row r="372" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G372" s="42"/>
     </row>
-    <row r="373" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G373" s="42"/>
     </row>
-    <row r="374" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G374" s="42"/>
     </row>
-    <row r="375" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G375" s="42"/>
     </row>
-    <row r="376" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:7" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="G376" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="L12:L13"/>
     <mergeCell ref="A14:J14"/>
@@ -9305,11 +9310,6 @@
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9318,41 +9318,41 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B11E31-8149-4845-BC35-72EC243C72CB}">
   <dimension ref="A1:J291"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="3.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="9" max="9" width="2.5703125" customWidth="1"/>
-    <col min="10" max="10" width="23.5703125" customWidth="1"/>
+    <col min="1" max="1" width="36.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" customWidth="1"/>
+    <col min="6" max="6" width="3.453125" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" customWidth="1"/>
+    <col min="8" max="8" width="2.7265625" customWidth="1"/>
+    <col min="9" max="9" width="2.54296875" customWidth="1"/>
+    <col min="10" max="10" width="23.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G1" s="1"/>
       <c r="I1" s="2"/>
       <c r="J1" s="184"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="237" t="s">
-        <v>266</v>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="186" t="s">
+        <v>264</v>
       </c>
       <c r="G2" s="1"/>
       <c r="I2" s="3"/>
       <c r="J2" s="185"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="I3" s="3"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" s="71" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="71" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="166" t="s">
         <v>228</v>
       </c>
@@ -9366,7 +9366,7 @@
       <c r="I4" s="166"/>
       <c r="J4" s="166"/>
     </row>
-    <row r="5" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="153" t="s">
         <v>208</v>
       </c>
@@ -9380,7 +9380,7 @@
       <c r="I5" s="78"/>
       <c r="J5" s="78"/>
     </row>
-    <row r="6" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="153" t="s">
         <v>209</v>
       </c>
@@ -9394,7 +9394,7 @@
       <c r="I6" s="78"/>
       <c r="J6" s="78"/>
     </row>
-    <row r="7" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="153"/>
       <c r="B7" s="76"/>
       <c r="C7" s="78"/>
@@ -9406,7 +9406,7 @@
       <c r="I7" s="78"/>
       <c r="J7" s="78"/>
     </row>
-    <row r="8" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="153"/>
       <c r="B8" s="76"/>
       <c r="C8" s="78"/>
@@ -9418,7 +9418,7 @@
       <c r="I8" s="78"/>
       <c r="J8" s="78"/>
     </row>
-    <row r="9" spans="1:10" s="29" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" s="29" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="167"/>
       <c r="C9" s="60"/>
       <c r="D9" s="60"/>
@@ -9429,7 +9429,7 @@
       <c r="I9" s="60"/>
       <c r="J9" s="60"/>
     </row>
-    <row r="10" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="168" t="s">
         <v>210</v>
       </c>
@@ -9443,7 +9443,7 @@
       <c r="I10" s="171"/>
       <c r="J10" s="171"/>
     </row>
-    <row r="11" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="67" t="s">
         <v>211</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="153" t="s">
         <v>229</v>
       </c>
@@ -9487,7 +9487,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="153" t="s">
         <v>231</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="153" t="s">
         <v>232</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="153" t="s">
         <v>233</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="153" t="s">
         <v>235</v>
       </c>
@@ -9561,25 +9561,25 @@
         <v>219</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="153" t="s">
         <v>236</v>
       </c>
       <c r="B17" s="76"/>
       <c r="C17" s="75"/>
       <c r="D17" s="75"/>
-      <c r="E17" s="233" t="s">
+      <c r="E17" s="245" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
       <c r="H17" s="173"/>
       <c r="I17" s="75"/>
       <c r="J17" s="75" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="153" t="s">
         <v>238</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="153" t="s">
         <v>239</v>
       </c>
@@ -9617,7 +9617,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="153" t="s">
         <v>241</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="153" t="s">
         <v>225</v>
       </c>
@@ -9653,7 +9653,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="153"/>
       <c r="B22" s="76"/>
       <c r="C22" s="78"/>
@@ -9665,7 +9665,7 @@
       <c r="I22" s="78"/>
       <c r="J22" s="75"/>
     </row>
-    <row r="23" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="159"/>
       <c r="B23" s="160"/>
       <c r="C23" s="161"/>
@@ -9677,7 +9677,7 @@
       <c r="I23" s="161"/>
       <c r="J23" s="161"/>
     </row>
-    <row r="24" spans="1:10" s="165" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" s="165" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="162" t="s">
         <v>227</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="29" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B25" s="167"/>
       <c r="C25" s="60"/>
       <c r="D25" s="60"/>
@@ -9704,7 +9704,7 @@
       <c r="I25" s="60"/>
       <c r="J25" s="60"/>
     </row>
-    <row r="26" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="71" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="67" t="s">
         <v>244</v>
       </c>
@@ -9731,20 +9731,20 @@
       <c r="I27" s="60"/>
       <c r="J27" s="60"/>
     </row>
-    <row r="28" spans="1:10" s="73" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="234" t="s">
+    <row r="28" spans="1:10" s="73" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="246" t="s">
         <v>245</v>
       </c>
-      <c r="B28" s="234"/>
+      <c r="B28" s="246"/>
       <c r="C28" s="175" t="s">
         <v>246</v>
       </c>
-      <c r="D28" s="234" t="s">
+      <c r="D28" s="246" t="s">
         <v>247</v>
       </c>
-      <c r="E28" s="234"/>
-      <c r="F28" s="234"/>
-      <c r="G28" s="234"/>
+      <c r="E28" s="246"/>
+      <c r="F28" s="246"/>
+      <c r="G28" s="246"/>
       <c r="I28" s="176" t="s">
         <v>246</v>
       </c>
@@ -9752,19 +9752,19 @@
         <v>219</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="73" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="235" t="s">
+    <row r="29" spans="1:10" s="73" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="247" t="s">
         <v>248</v>
       </c>
-      <c r="B29" s="235"/>
-      <c r="D29" s="236">
+      <c r="B29" s="247"/>
+      <c r="D29" s="248">
         <v>113.8</v>
       </c>
-      <c r="E29" s="236"/>
-      <c r="F29" s="236"/>
-      <c r="G29" s="236"/>
-    </row>
-    <row r="30" spans="1:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="248"/>
+      <c r="F29" s="248"/>
+      <c r="G29" s="248"/>
+    </row>
+    <row r="30" spans="1:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="60"/>
       <c r="C30" s="60"/>
       <c r="D30" s="60"/>
@@ -9775,7 +9775,7 @@
       <c r="I30" s="60"/>
       <c r="J30" s="60"/>
     </row>
-    <row r="31" spans="1:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="60"/>
       <c r="C31" s="60"/>
       <c r="D31" s="60"/>
@@ -9786,7 +9786,7 @@
       <c r="I31" s="60"/>
       <c r="J31" s="60"/>
     </row>
-    <row r="32" spans="1:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="60"/>
       <c r="C32" s="60"/>
       <c r="D32" s="60"/>
@@ -9797,7 +9797,7 @@
       <c r="I32" s="60"/>
       <c r="J32" s="60"/>
     </row>
-    <row r="33" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="60"/>
       <c r="C33" s="60"/>
       <c r="D33" s="60"/>
@@ -9808,7 +9808,7 @@
       <c r="I33" s="60"/>
       <c r="J33" s="60"/>
     </row>
-    <row r="34" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="60"/>
       <c r="C34" s="60"/>
       <c r="D34" s="60"/>
@@ -9819,7 +9819,7 @@
       <c r="I34" s="60"/>
       <c r="J34" s="60"/>
     </row>
-    <row r="35" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="60"/>
       <c r="C35" s="60"/>
       <c r="D35" s="60"/>
@@ -9830,7 +9830,7 @@
       <c r="I35" s="60"/>
       <c r="J35" s="60"/>
     </row>
-    <row r="36" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="60"/>
       <c r="C36" s="60"/>
       <c r="D36" s="60"/>
@@ -9841,7 +9841,7 @@
       <c r="I36" s="60"/>
       <c r="J36" s="60"/>
     </row>
-    <row r="37" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="60"/>
       <c r="C37" s="60"/>
       <c r="D37" s="60"/>
@@ -9852,7 +9852,7 @@
       <c r="I37" s="60"/>
       <c r="J37" s="60"/>
     </row>
-    <row r="38" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="60"/>
       <c r="C38" s="60"/>
       <c r="D38" s="60"/>
@@ -9863,7 +9863,7 @@
       <c r="I38" s="60"/>
       <c r="J38" s="60"/>
     </row>
-    <row r="39" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="60"/>
       <c r="C39" s="60"/>
       <c r="D39" s="60"/>
@@ -9874,7 +9874,7 @@
       <c r="I39" s="60"/>
       <c r="J39" s="60"/>
     </row>
-    <row r="40" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="60"/>
       <c r="C40" s="60"/>
       <c r="D40" s="60"/>
@@ -9885,7 +9885,7 @@
       <c r="I40" s="60"/>
       <c r="J40" s="60"/>
     </row>
-    <row r="41" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="60"/>
       <c r="C41" s="60"/>
       <c r="D41" s="60"/>
@@ -9896,7 +9896,7 @@
       <c r="I41" s="60"/>
       <c r="J41" s="60"/>
     </row>
-    <row r="42" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="60"/>
       <c r="C42" s="60"/>
       <c r="D42" s="60"/>
@@ -9907,7 +9907,7 @@
       <c r="I42" s="60"/>
       <c r="J42" s="60"/>
     </row>
-    <row r="43" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="60"/>
       <c r="C43" s="60"/>
       <c r="D43" s="60"/>
@@ -9918,7 +9918,7 @@
       <c r="I43" s="60"/>
       <c r="J43" s="60"/>
     </row>
-    <row r="44" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="60"/>
       <c r="C44" s="60"/>
       <c r="D44" s="60"/>
@@ -9929,7 +9929,7 @@
       <c r="I44" s="60"/>
       <c r="J44" s="60"/>
     </row>
-    <row r="45" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="60"/>
       <c r="C45" s="60"/>
       <c r="D45" s="60"/>
@@ -9940,7 +9940,7 @@
       <c r="I45" s="60"/>
       <c r="J45" s="60"/>
     </row>
-    <row r="46" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="60"/>
       <c r="C46" s="60"/>
       <c r="D46" s="60"/>
@@ -9951,7 +9951,7 @@
       <c r="I46" s="60"/>
       <c r="J46" s="60"/>
     </row>
-    <row r="47" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="60"/>
       <c r="C47" s="60"/>
       <c r="D47" s="60"/>
@@ -9962,7 +9962,7 @@
       <c r="I47" s="60"/>
       <c r="J47" s="60"/>
     </row>
-    <row r="48" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="60" t="s">
         <v>249</v>
       </c>
@@ -9977,7 +9977,7 @@
       <c r="I48" s="60"/>
       <c r="J48" s="60"/>
     </row>
-    <row r="49" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="60"/>
       <c r="C49" s="60"/>
       <c r="D49" s="60"/>
@@ -9988,7 +9988,7 @@
       <c r="I49" s="60"/>
       <c r="J49" s="60"/>
     </row>
-    <row r="50" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="60"/>
       <c r="C50" s="60"/>
       <c r="D50" s="60"/>
@@ -9999,7 +9999,7 @@
       <c r="I50" s="60"/>
       <c r="J50" s="60"/>
     </row>
-    <row r="51" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="60"/>
       <c r="C51" s="60"/>
       <c r="D51" s="60"/>
@@ -10010,7 +10010,7 @@
       <c r="I51" s="60"/>
       <c r="J51" s="60"/>
     </row>
-    <row r="52" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="60"/>
       <c r="C52" s="60"/>
       <c r="D52" s="60"/>
@@ -10021,7 +10021,7 @@
       <c r="I52" s="60"/>
       <c r="J52" s="60"/>
     </row>
-    <row r="53" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="60"/>
       <c r="C53" s="60"/>
       <c r="D53" s="60"/>
@@ -10032,7 +10032,7 @@
       <c r="I53" s="60"/>
       <c r="J53" s="60"/>
     </row>
-    <row r="54" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="60"/>
       <c r="C54" s="60"/>
       <c r="D54" s="60"/>
@@ -10043,7 +10043,7 @@
       <c r="I54" s="60"/>
       <c r="J54" s="60"/>
     </row>
-    <row r="55" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="60"/>
       <c r="C55" s="60"/>
       <c r="D55" s="60"/>
@@ -10054,7 +10054,7 @@
       <c r="I55" s="60"/>
       <c r="J55" s="60"/>
     </row>
-    <row r="56" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="60"/>
       <c r="C56" s="60"/>
       <c r="D56" s="60"/>
@@ -10065,7 +10065,7 @@
       <c r="I56" s="60"/>
       <c r="J56" s="60"/>
     </row>
-    <row r="57" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="60"/>
       <c r="C57" s="60"/>
       <c r="D57" s="60"/>
@@ -10076,7 +10076,7 @@
       <c r="I57" s="60"/>
       <c r="J57" s="60"/>
     </row>
-    <row r="58" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="60"/>
       <c r="C58" s="60"/>
       <c r="D58" s="60"/>
@@ -10087,7 +10087,7 @@
       <c r="I58" s="60"/>
       <c r="J58" s="60"/>
     </row>
-    <row r="59" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="60"/>
       <c r="C59" s="60"/>
       <c r="D59" s="60"/>
@@ -10098,7 +10098,7 @@
       <c r="I59" s="60"/>
       <c r="J59" s="60"/>
     </row>
-    <row r="60" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="60"/>
       <c r="C60" s="60"/>
       <c r="D60" s="60"/>
@@ -10109,7 +10109,7 @@
       <c r="I60" s="60"/>
       <c r="J60" s="60"/>
     </row>
-    <row r="61" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="60"/>
       <c r="C61" s="60" t="s">
         <v>250</v>
@@ -10122,7 +10122,7 @@
       <c r="I61" s="60"/>
       <c r="J61" s="60"/>
     </row>
-    <row r="62" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="60"/>
       <c r="C62" s="60"/>
       <c r="D62" s="60"/>
@@ -10133,7 +10133,7 @@
       <c r="I62" s="60"/>
       <c r="J62" s="60"/>
     </row>
-    <row r="63" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="60"/>
       <c r="C63" s="60"/>
       <c r="D63" s="60"/>
@@ -10144,7 +10144,7 @@
       <c r="I63" s="60"/>
       <c r="J63" s="60"/>
     </row>
-    <row r="64" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="60"/>
       <c r="C64" s="60"/>
       <c r="D64" s="60"/>
@@ -10155,7 +10155,7 @@
       <c r="I64" s="60"/>
       <c r="J64" s="60"/>
     </row>
-    <row r="65" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="60"/>
       <c r="C65" s="60"/>
       <c r="D65" s="60"/>
@@ -10166,7 +10166,7 @@
       <c r="I65" s="60"/>
       <c r="J65" s="60"/>
     </row>
-    <row r="66" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="60"/>
       <c r="C66" s="60"/>
       <c r="D66" s="60"/>
@@ -10177,7 +10177,7 @@
       <c r="I66" s="60"/>
       <c r="J66" s="60"/>
     </row>
-    <row r="67" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="60"/>
       <c r="C67" s="60"/>
       <c r="D67" s="60"/>
@@ -10188,7 +10188,7 @@
       <c r="I67" s="60"/>
       <c r="J67" s="60"/>
     </row>
-    <row r="68" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="60"/>
       <c r="C68" s="60"/>
       <c r="D68" s="60"/>
@@ -10199,7 +10199,7 @@
       <c r="I68" s="60"/>
       <c r="J68" s="60"/>
     </row>
-    <row r="69" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="60"/>
       <c r="C69" s="60"/>
       <c r="D69" s="60"/>
@@ -10210,7 +10210,7 @@
       <c r="I69" s="60"/>
       <c r="J69" s="60"/>
     </row>
-    <row r="70" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="60"/>
       <c r="C70" s="60"/>
       <c r="D70" s="60"/>
@@ -10221,7 +10221,7 @@
       <c r="I70" s="60"/>
       <c r="J70" s="60"/>
     </row>
-    <row r="71" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B71" s="60"/>
       <c r="C71" s="60"/>
       <c r="D71" s="60"/>
@@ -10232,7 +10232,7 @@
       <c r="I71" s="60"/>
       <c r="J71" s="60"/>
     </row>
-    <row r="72" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="60"/>
       <c r="C72" s="60"/>
       <c r="D72" s="60"/>
@@ -10243,7 +10243,7 @@
       <c r="I72" s="60"/>
       <c r="J72" s="60"/>
     </row>
-    <row r="73" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="60"/>
       <c r="C73" s="60"/>
       <c r="D73" s="60"/>
@@ -10254,7 +10254,7 @@
       <c r="I73" s="60"/>
       <c r="J73" s="60"/>
     </row>
-    <row r="74" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="60"/>
       <c r="C74" s="60"/>
       <c r="D74" s="60"/>
@@ -10265,7 +10265,7 @@
       <c r="I74" s="60"/>
       <c r="J74" s="60"/>
     </row>
-    <row r="75" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="60"/>
       <c r="C75" s="60"/>
       <c r="D75" s="60"/>
@@ -10276,7 +10276,7 @@
       <c r="I75" s="60"/>
       <c r="J75" s="60"/>
     </row>
-    <row r="76" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="60"/>
       <c r="C76" s="60"/>
       <c r="D76" s="60"/>
@@ -10287,7 +10287,7 @@
       <c r="I76" s="60"/>
       <c r="J76" s="60"/>
     </row>
-    <row r="77" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B77" s="60"/>
       <c r="C77" s="60"/>
       <c r="D77" s="60"/>
@@ -10298,7 +10298,7 @@
       <c r="I77" s="60"/>
       <c r="J77" s="60"/>
     </row>
-    <row r="78" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="60"/>
       <c r="C78" s="60"/>
       <c r="D78" s="60"/>
@@ -10309,7 +10309,7 @@
       <c r="I78" s="60"/>
       <c r="J78" s="60"/>
     </row>
-    <row r="79" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="60"/>
       <c r="C79" s="60"/>
       <c r="D79" s="60"/>
@@ -10320,7 +10320,7 @@
       <c r="I79" s="60"/>
       <c r="J79" s="60"/>
     </row>
-    <row r="80" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="60"/>
       <c r="C80" s="60"/>
       <c r="D80" s="60"/>
@@ -10331,7 +10331,7 @@
       <c r="I80" s="60"/>
       <c r="J80" s="60"/>
     </row>
-    <row r="81" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="60"/>
       <c r="C81" s="60"/>
       <c r="D81" s="60"/>
@@ -10342,7 +10342,7 @@
       <c r="I81" s="60"/>
       <c r="J81" s="60"/>
     </row>
-    <row r="82" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="60"/>
       <c r="C82" s="60"/>
       <c r="D82" s="60"/>
@@ -10353,7 +10353,7 @@
       <c r="I82" s="60"/>
       <c r="J82" s="60"/>
     </row>
-    <row r="83" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B83" s="60"/>
       <c r="C83" s="60"/>
       <c r="D83" s="60"/>
@@ -10364,7 +10364,7 @@
       <c r="I83" s="60"/>
       <c r="J83" s="60"/>
     </row>
-    <row r="84" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="60"/>
       <c r="C84" s="60"/>
       <c r="D84" s="60"/>
@@ -10375,7 +10375,7 @@
       <c r="I84" s="60"/>
       <c r="J84" s="60"/>
     </row>
-    <row r="85" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="60"/>
       <c r="C85" s="60"/>
       <c r="D85" s="60"/>
@@ -10386,7 +10386,7 @@
       <c r="I85" s="60"/>
       <c r="J85" s="60"/>
     </row>
-    <row r="86" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="60"/>
       <c r="C86" s="60"/>
       <c r="D86" s="60"/>
@@ -10397,7 +10397,7 @@
       <c r="I86" s="60"/>
       <c r="J86" s="60"/>
     </row>
-    <row r="87" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="60"/>
       <c r="C87" s="60"/>
       <c r="D87" s="60"/>
@@ -10408,7 +10408,7 @@
       <c r="I87" s="60"/>
       <c r="J87" s="60"/>
     </row>
-    <row r="88" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="60"/>
       <c r="C88" s="60"/>
       <c r="D88" s="60"/>
@@ -10419,7 +10419,7 @@
       <c r="I88" s="60"/>
       <c r="J88" s="60"/>
     </row>
-    <row r="89" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="60"/>
       <c r="C89" s="60"/>
       <c r="D89" s="60"/>
@@ -10430,7 +10430,7 @@
       <c r="I89" s="60"/>
       <c r="J89" s="60"/>
     </row>
-    <row r="90" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B90" s="60"/>
       <c r="C90" s="60"/>
       <c r="D90" s="60"/>
@@ -10441,7 +10441,7 @@
       <c r="I90" s="60"/>
       <c r="J90" s="60"/>
     </row>
-    <row r="91" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B91" s="60"/>
       <c r="C91" s="60"/>
       <c r="D91" s="60"/>
@@ -10452,7 +10452,7 @@
       <c r="I91" s="60"/>
       <c r="J91" s="60"/>
     </row>
-    <row r="92" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B92" s="60"/>
       <c r="C92" s="60"/>
       <c r="D92" s="60"/>
@@ -10463,7 +10463,7 @@
       <c r="I92" s="60"/>
       <c r="J92" s="60"/>
     </row>
-    <row r="93" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B93" s="60"/>
       <c r="C93" s="60"/>
       <c r="D93" s="60"/>
@@ -10474,204 +10474,204 @@
       <c r="I93" s="60"/>
       <c r="J93" s="60"/>
     </row>
-    <row r="94" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B94" s="60"/>
     </row>
-    <row r="95" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B95" s="60"/>
     </row>
-    <row r="96" spans="2:10" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:10" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B96" s="60"/>
     </row>
-    <row r="97" spans="2:2" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B97" s="60"/>
     </row>
-    <row r="98" spans="2:2" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="60"/>
     </row>
-    <row r="99" spans="2:2" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B99" s="60"/>
     </row>
-    <row r="100" spans="2:2" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B100" s="60"/>
     </row>
-    <row r="101" spans="2:2" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:2" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B101" s="60"/>
     </row>
-    <row r="102" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="60"/>
     </row>
-    <row r="103" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="60"/>
     </row>
-    <row r="104" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="60"/>
     </row>
-    <row r="105" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="60"/>
     </row>
-    <row r="106" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="60"/>
     </row>
-    <row r="107" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B107" s="60"/>
     </row>
-    <row r="108" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B108" s="60"/>
     </row>
-    <row r="109" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B109" s="60"/>
     </row>
-    <row r="110" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B110" s="60"/>
     </row>
-    <row r="111" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B111" s="60"/>
     </row>
-    <row r="112" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B112" s="60"/>
     </row>
-    <row r="113" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B113" s="60"/>
     </row>
-    <row r="114" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B114" s="60"/>
     </row>
-    <row r="115" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B115" s="60"/>
     </row>
-    <row r="116" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B116" s="60"/>
     </row>
-    <row r="117" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B117" s="60"/>
     </row>
-    <row r="118" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B118" s="60"/>
     </row>
-    <row r="119" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B119" s="60"/>
       <c r="J119" s="179" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="120" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B120" s="60"/>
     </row>
-    <row r="121" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B121" s="60"/>
     </row>
-    <row r="122" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B122" s="60"/>
     </row>
-    <row r="123" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B123" s="60"/>
     </row>
-    <row r="124" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B124" s="60"/>
     </row>
-    <row r="125" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B125" s="60"/>
     </row>
-    <row r="126" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B126" s="60"/>
     </row>
-    <row r="127" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B127" s="60"/>
     </row>
-    <row r="128" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B128" s="60"/>
     </row>
-    <row r="129" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B129" s="60"/>
     </row>
-    <row r="130" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B130" s="60"/>
     </row>
-    <row r="131" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B131" s="60"/>
     </row>
-    <row r="132" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B132" s="60"/>
     </row>
-    <row r="133" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B133" s="60"/>
     </row>
-    <row r="134" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B134" s="60"/>
     </row>
-    <row r="135" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B135" s="60"/>
     </row>
-    <row r="136" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B136" s="60"/>
     </row>
-    <row r="137" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B137" s="60"/>
     </row>
-    <row r="138" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B138" s="60"/>
     </row>
-    <row r="139" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B139" s="60"/>
     </row>
-    <row r="140" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B140" s="60"/>
     </row>
-    <row r="141" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B141" s="60"/>
     </row>
-    <row r="142" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B142" s="60"/>
     </row>
-    <row r="143" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="144" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="145" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="146" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="147" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="148" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="149" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="150" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="151" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="152" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="153" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="154" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="155" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="156" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B156" s="29" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="157" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="158" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="159" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="160" spans="2:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="161" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="162" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="163" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="164" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="165" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="166" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="167" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="168" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="169" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="170" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B170" s="115" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="171" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="172" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="173" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="174" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="175" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="176" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A176" s="29" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="177" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="178" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A178" s="58" t="s">
         <v>255</v>
       </c>
@@ -10679,123 +10679,123 @@
         <v>256</v>
       </c>
     </row>
-    <row r="179" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="180" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="181" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="182" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A182" s="29" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="183" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="193" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="194" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="195" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="196" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="197" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="198" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="199" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="200" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="201" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="202" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="203" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="204" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="205" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="206" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="207" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="208" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="209" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="210" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="211" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="212" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="213" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="214" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="215" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="216" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="217" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="218" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="219" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="220" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="221" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="222" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="223" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="224" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="225" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="226" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="227" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="228" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="229" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="230" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="231" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="232" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="233" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="234" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="235" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="236" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="237" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="238" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="239" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="240" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="241" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="242" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="243" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="244" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="245" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="246" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="247" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="248" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="249" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="250" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="251" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="252" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="253" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="254" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="255" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="256" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="257" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="258" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="259" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="260" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="261" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="262" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="263" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="264" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="265" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="266" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="267" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="268" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="269" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="270" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="271" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="272" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="273" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="274" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="275" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="276" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="277" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="278" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="279" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="280" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="281" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="282" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="283" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="284" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="285" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="286" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="287" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="288" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="289" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="290" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="291" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="184" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="185" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="186" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="187" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="188" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="189" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="190" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="191" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="192" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="193" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="194" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="195" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="196" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="197" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="198" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="199" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="200" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="201" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="202" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="203" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="204" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="205" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="206" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="207" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="208" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="209" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="210" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="211" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="212" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="213" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="214" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="215" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="216" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="217" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="218" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="219" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="220" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="221" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="222" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="223" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="224" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="225" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="226" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="227" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="228" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="229" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="230" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="231" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="232" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="233" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="234" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="235" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="236" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="237" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="238" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="239" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="240" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="241" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="242" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="243" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="244" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="245" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="246" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="247" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="248" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="249" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="250" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="251" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="252" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="253" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="254" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="255" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="256" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="257" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="258" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="259" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="260" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="261" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="262" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="263" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="264" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="265" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="266" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="267" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="268" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="269" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="270" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="271" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="272" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="273" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="274" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="275" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="276" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="277" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="278" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="279" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="280" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="281" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="282" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="283" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="284" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="285" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="286" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="287" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="288" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="289" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="290" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="291" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="E17:G17"/>
